--- a/FICO/3S_FICO.xlsx
+++ b/FICO/3S_FICO.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22296" windowHeight="8376" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="10K_Sources" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Audit_Fixes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3 Statement Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -67,7 +67,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Statement Model'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Statement Model'!$A$1:$N$104</definedName>
   </definedNames>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -284,7 +284,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -313,6 +313,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -534,20 +539,14 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="26" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,775 +595,93 @@
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
+          <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Earnings (2012 - 2016)</a:t>
+              <a:t>FICO Revenue FY2021–2030</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
     </title>
     <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
+      <lineChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'3 Statement Model'!$B$121</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v xml:space="preserve"> Revenue </v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
           <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
             <a:ln>
-              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
-          <invertIfNegative val="0"/>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
           <cat>
             <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
+              <f>'3 Statement Model'!$E$2:$N$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'3 Statement Model'!$E$121:$I$121</f>
+              <f>'3 Statement Model'!$E$24:$N$24</f>
             </numRef>
           </val>
         </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'3 Statement Model'!$B$122</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v xml:space="preserve"> Gross Profit </v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'3 Statement Model'!$E$122:$I$122</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'3 Statement Model'!$B$123</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v xml:space="preserve"> Earning Before Tax </v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'3 Statement Model'!$E$123:$I$123</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="60"/>
-        <axId val="626472968"/>
-        <axId val="626472640"/>
-      </barChart>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
-        <axId val="626472968"/>
+        <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
+        <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="626472640"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
+        <crossAx val="100"/>
         <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
-        <axId val="626472640"/>
+        <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <delete val="0"/>
         <axPos val="l"/>
-        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="626472968"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
+        <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
+      <legendPos val="r"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Cash Flows (2012</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t xml:space="preserve"> - 2016)</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="1"/>
-          <order val="0"/>
-          <tx>
-            <v>Operating</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'3 Statement Model'!$E$125:$I$125</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="1"/>
-          <tx>
-            <v>Investing</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'3 Statement Model'!$E$126:$I$126</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="2"/>
-          <tx>
-            <v>FInancing</v>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <numRef>
-              <f>'3 Statement Model'!$E$2:$I$2</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="5"/>
-                <pt idx="0">
-                  <v>2012</v>
-                </pt>
-                <pt idx="1">
-                  <v>2013</v>
-                </pt>
-                <pt idx="2">
-                  <v>2014</v>
-                </pt>
-                <pt idx="3">
-                  <v>2015</v>
-                </pt>
-                <pt idx="4">
-                  <v>2016</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'3 Statement Model'!$E$127:$I$127</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <overlap val="100"/>
-        <axId val="626556256"/>
-        <axId val="626558224"/>
-      </barChart>
-      <catAx>
-        <axId val="626556256"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="626558224"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="626558224"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </txPr>
-        <crossAx val="626556256"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Open Sans" panose="020B0606030504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
+  <oneCellAnchor>
     <from>
-      <col>1</col>
-      <colOff>570970</colOff>
-      <row>105</row>
-      <rowOff>17991</rowOff>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
     </from>
-    <to>
-      <col>6</col>
-      <colOff>485245</colOff>
-      <row>118</row>
-      <rowOff>165101</rowOff>
-    </to>
+    <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1378,34 +695,7 @@
       </a:graphic>
     </graphicFrame>
     <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>42333</colOff>
-      <row>105</row>
-      <rowOff>17991</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>413809</colOff>
-      <row>118</row>
-      <rowOff>165101</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1676,1712 +966,349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="92" t="inlineStr">
         <is>
-          <t>FICO 3-Statement — 10-K source map</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fair Isaac Corporation (FICO) | CIK 0000814547 | FYE September 30 | Units: USD thousands</t>
+          <t>Errors found and fixed</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Click the FY2025 10-K link for each line. Naming differences (e.g. OpEx) are explained in column E.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="93" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>Model / CFI label</t>
-        </is>
-      </c>
-      <c r="C5" s="93" t="inlineStr">
-        <is>
-          <t>CFI cell/row</t>
-        </is>
-      </c>
-      <c r="D5" s="93" t="inlineStr">
-        <is>
-          <t>FICO 10-K label (as printed)</t>
-        </is>
-      </c>
-      <c r="E5" s="93" t="inlineStr">
-        <is>
-          <t>Naming / mapping note</t>
-        </is>
-      </c>
-      <c r="F5" s="93" t="inlineStr">
-        <is>
-          <t>10-K statement section</t>
-        </is>
-      </c>
-      <c r="G5" s="93" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="H5" s="93" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="I5" s="93" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="J5" s="93" t="inlineStr">
-        <is>
-          <t>FY2025 10-K URL</t>
-        </is>
-      </c>
-      <c r="K5" s="93" t="inlineStr">
-        <is>
-          <t>FY2024 10-K URL</t>
-        </is>
-      </c>
-      <c r="L5" s="93" t="inlineStr">
-        <is>
-          <t>FY2023 10-K URL</t>
-        </is>
-      </c>
-      <c r="M5" s="93" t="inlineStr">
-        <is>
-          <t>XBRL / derivation</t>
+      <c r="A3" s="93" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B3" s="93" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="C3" s="93" t="inlineStr">
+        <is>
+          <t>Fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3S forecast COGS%</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Was 37% (CFI sample)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Now 17.77% from FY25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3S forecast SG&amp;A/R&amp;D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Was $25k / $10k</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B6" s="94" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="C6" s="94" t="inlineStr">
-        <is>
-          <t>3S!row24 / DCF driver base</t>
-        </is>
-      </c>
-      <c r="D6" s="94" t="inlineStr">
-        <is>
-          <t>Revenues</t>
-        </is>
-      </c>
-      <c r="E6" s="94" t="inlineStr">
-        <is>
-          <t>Same meaning. 10-K Consolidated Statements of Income: 'Revenues'.</t>
-        </is>
-      </c>
-      <c r="F6" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G6" s="94" t="n">
-        <v>1513557</v>
-      </c>
-      <c r="H6" s="94" t="n">
-        <v>1717526</v>
-      </c>
-      <c r="I6" s="94" t="n">
-        <v>1990869</v>
-      </c>
-      <c r="J6" s="95" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3S forecast tax</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Was 28%</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Now 18.77% FY25 ETR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3S AR / Inv days</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Was 18 / 73</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Now ~97 / 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>3S Capex forecast</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Was ~15k sample</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Now from FY25 39,407 growing 8%/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3S year headers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Formulas blank pre-calc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hardcoded 2021–2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DCF Year-1 EBIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Path anchored to FY25 OpInc 924,850</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DCF D&amp;A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Used ~18k (0.8% rev)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Anchored to FY25 D&amp;A 14,952</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DCF years</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Unclear / missing FY25 base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FY25 actuals in row 16; forecast 2026–2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DCF Capex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Flat 39,407</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Grows 8%/yr with investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DCF EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>25x → huge TV vs PG</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Set 22x; still show PG / multiple / average</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DCF blanks</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Written as computed values + chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="B18" s="94" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
       </c>
-      <c r="K6" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L6" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M6" s="94" t="inlineStr">
-        <is>
-          <t>RevenueFromContractWithCustomerExcludingAssessedTax</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B7" s="94" t="inlineStr">
-        <is>
-          <t>COGS / Cost of Goods Sold</t>
-        </is>
-      </c>
-      <c r="C7" s="94" t="inlineStr">
-        <is>
-          <t>3S!row25</t>
-        </is>
-      </c>
-      <c r="D7" s="94" t="inlineStr">
-        <is>
-          <t>Cost of revenues</t>
-        </is>
-      </c>
-      <c r="E7" s="94" t="inlineStr">
-        <is>
-          <t>CFI says COGS; FICO 10-K labels it 'Cost of revenues' (same economic line).</t>
-        </is>
-      </c>
-      <c r="F7" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G7" s="94" t="n">
-        <v>311053</v>
-      </c>
-      <c r="H7" s="94" t="n">
-        <v>348206</v>
-      </c>
-      <c r="I7" s="94" t="n">
-        <v>353722</v>
-      </c>
-      <c r="J7" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K7" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L7" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M7" s="94" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF OpEx</t>
-        </is>
-      </c>
-      <c r="B8" s="94" t="inlineStr">
-        <is>
-          <t>SG&amp;A (CFI: Salaries and Benefits)</t>
-        </is>
-      </c>
-      <c r="C8" s="94" t="inlineStr">
-        <is>
-          <t>3S!row28</t>
-        </is>
-      </c>
-      <c r="D8" s="94" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative</t>
-        </is>
-      </c>
-      <c r="E8" s="94" t="inlineStr">
-        <is>
-          <t>NAMING DIFFERS. CFI template line is 'Salaries and Benefits'. FICO 10-K has no 'Salaries' line — map FICO SG&amp;A here. OpEx in FICO ≈ SG&amp;A + R&amp;D (below).</t>
-        </is>
-      </c>
-      <c r="F8" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G8" s="94" t="n">
-        <v>400565</v>
-      </c>
-      <c r="H8" s="94" t="n">
-        <v>462834</v>
-      </c>
-      <c r="I8" s="94" t="n">
-        <v>513028</v>
-      </c>
-      <c r="J8" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K8" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L8" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M8" s="94" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF OpEx</t>
-        </is>
-      </c>
-      <c r="B9" s="94" t="inlineStr">
-        <is>
-          <t>R&amp;D (CFI: Rent and Overhead)</t>
-        </is>
-      </c>
-      <c r="C9" s="94" t="inlineStr">
-        <is>
-          <t>3S!row29</t>
-        </is>
-      </c>
-      <c r="D9" s="94" t="inlineStr">
-        <is>
-          <t>Research and development</t>
-        </is>
-      </c>
-      <c r="E9" s="94" t="inlineStr">
-        <is>
-          <t>NAMING DIFFERS. CFI 'Rent and Overhead' is a placeholder opex bucket. FICO maps R&amp;D expense into that row. Combined SG&amp;A+R&amp;D = operating expenses excl. COGS/D&amp;A.</t>
-        </is>
-      </c>
-      <c r="F9" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G9" s="94" t="n">
-        <v>159950</v>
-      </c>
-      <c r="H9" s="94" t="n">
-        <v>171940</v>
-      </c>
-      <c r="I9" s="94" t="n">
-        <v>188347</v>
-      </c>
-      <c r="J9" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K9" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L9" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M9" s="94" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopmentExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="94" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B10" s="94" t="inlineStr">
-        <is>
-          <t>Operating Expenses (SG&amp;A + R&amp;D)</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="inlineStr">
-        <is>
-          <t>used inside DCF EBIT build</t>
-        </is>
-      </c>
-      <c r="D10" s="94" t="inlineStr">
-        <is>
-          <t>Selling, general and administrative + Research and development</t>
-        </is>
-      </c>
-      <c r="E10" s="94" t="inlineStr">
-        <is>
-          <t>FICO does not print a single 'Operating expenses' total for SG&amp;A+R&amp;D. Sum the two 10-K lines. Do NOT confuse with 'Cost of revenues'.</t>
-        </is>
-      </c>
-      <c r="F10" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G10" s="94" t="n">
-        <v>560515</v>
-      </c>
-      <c r="H10" s="94" t="n">
-        <v>634774</v>
-      </c>
-      <c r="I10" s="94" t="n">
-        <v>701375</v>
-      </c>
-      <c r="J10" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K10" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L10" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M10" s="94" t="inlineStr">
-        <is>
-          <t>SG&amp;A + R&amp;D (derived)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="94" t="inlineStr">
-        <is>
-          <t>DCF</t>
-        </is>
-      </c>
-      <c r="B11" s="94" t="inlineStr">
-        <is>
-          <t>EBIT / Operating income</t>
-        </is>
-      </c>
-      <c r="C11" s="94" t="inlineStr">
-        <is>
-          <t>DCF!E21 (and forecast)</t>
-        </is>
-      </c>
-      <c r="D11" s="94" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="E11" s="94" t="inlineStr">
-        <is>
-          <t>CFI/DCF 'EBIT' ≈ FICO 'Operating income' on the income statement.</t>
-        </is>
-      </c>
-      <c r="F11" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G11" s="94" t="n">
-        <v>642830</v>
-      </c>
-      <c r="H11" s="94" t="n">
-        <v>733629</v>
-      </c>
-      <c r="I11" s="94" t="n">
-        <v>924850</v>
-      </c>
-      <c r="J11" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K11" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L11" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M11" s="94" t="inlineStr">
-        <is>
-          <t>OperatingIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B12" s="94" t="inlineStr">
-        <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="C12" s="94" t="inlineStr">
-        <is>
-          <t>3S!row31</t>
-        </is>
-      </c>
-      <c r="D12" s="94" t="inlineStr">
-        <is>
-          <t>Interest expense, net</t>
-        </is>
-      </c>
-      <c r="E12" s="94" t="inlineStr">
-        <is>
-          <t>10-K presents 'Interest expense, net' (interest expense netted with interest income). Use that printed line, not gross InterestExpense alone when they diverge.</t>
-        </is>
-      </c>
-      <c r="F12" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G12" s="94" t="n">
-        <v>95546</v>
-      </c>
-      <c r="H12" s="94" t="n">
-        <v>105638</v>
-      </c>
-      <c r="I12" s="94" t="n">
-        <v>133647</v>
-      </c>
-      <c r="J12" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K12" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L12" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M12" s="94" t="inlineStr">
-        <is>
-          <t>Interest expense, net (10-K IS line)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B13" s="94" t="inlineStr">
-        <is>
-          <t>Tax Expense / Cash Taxes rate</t>
-        </is>
-      </c>
-      <c r="C13" s="94" t="inlineStr">
-        <is>
-          <t>3S!row35; DCF!D5 tax rate</t>
-        </is>
-      </c>
-      <c r="D13" s="94" t="inlineStr">
-        <is>
-          <t>Provision for income taxes</t>
-        </is>
-      </c>
-      <c r="E13" s="94" t="inlineStr">
-        <is>
-          <t>Tax expense from income statement. DCF cash-tax rate uses FY25 tax / pretax approx.</t>
-        </is>
-      </c>
-      <c r="F13" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income and Comprehensive Income</t>
-        </is>
-      </c>
-      <c r="G13" s="94" t="n">
-        <v>124249</v>
-      </c>
-      <c r="H13" s="94" t="n">
-        <v>129214</v>
-      </c>
-      <c r="I13" s="94" t="n">
-        <v>150649</v>
-      </c>
-      <c r="J13" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K13" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L13" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M13" s="94" t="inlineStr">
-        <is>
-          <t>IncomeTaxExpenseBenefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B14" s="94" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="C14" s="94" t="inlineStr">
-        <is>
-          <t>3S!row36/62</t>
-        </is>
-      </c>
-      <c r="D14" s="94" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="E14" s="94" t="inlineStr">
-        <is>
-          <t>Same naming.</t>
-        </is>
-      </c>
-      <c r="F14" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Income / Cash Flows</t>
-        </is>
-      </c>
-      <c r="G14" s="94" t="n">
-        <v>429375</v>
-      </c>
-      <c r="H14" s="94" t="n">
-        <v>512811</v>
-      </c>
-      <c r="I14" s="94" t="n">
-        <v>651946</v>
-      </c>
-      <c r="J14" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K14" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L14" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M14" s="94" t="inlineStr">
-        <is>
-          <t>NetIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B15" s="94" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C15" s="94" t="inlineStr">
-        <is>
-          <t>3S!row30/63; DCF!E23</t>
-        </is>
-      </c>
-      <c r="D15" s="94" t="inlineStr">
-        <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="E15" s="94" t="inlineStr">
-        <is>
-          <t>From Consolidated Statements of Cash Flows (add-back).</t>
-        </is>
-      </c>
-      <c r="F15" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows</t>
-        </is>
-      </c>
-      <c r="G15" s="94" t="n">
-        <v>14638</v>
-      </c>
-      <c r="H15" s="94" t="n">
-        <v>13827</v>
-      </c>
-      <c r="I15" s="94" t="n">
-        <v>14952</v>
-      </c>
-      <c r="J15" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K15" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L15" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M15" s="94" t="inlineStr">
-        <is>
-          <t>DepreciationDepletionAndAmortization</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B16" s="94" t="inlineStr">
-        <is>
-          <t>CapEx</t>
-        </is>
-      </c>
-      <c r="C16" s="94" t="inlineStr">
-        <is>
-          <t>3S!row68; DCF!D15 / row24</t>
-        </is>
-      </c>
-      <c r="D16" s="94" t="inlineStr">
-        <is>
-          <t>Purchases of property and equipment + Capitalized internal-use software costs</t>
-        </is>
-      </c>
-      <c r="E16" s="94" t="inlineStr">
-        <is>
-          <t>NAMING / SCOPE. CFI 'Investments in Property &amp; Equipment' / DCF Capex. FICO CapEx for modeling = PPE purchases + capitalized internal-use software (both in CF investing). FY25: 8,922 + 30,485 = 39,407.</t>
-        </is>
-      </c>
-      <c r="F16" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows — Investing activities</t>
-        </is>
-      </c>
-      <c r="G16" s="94" t="n">
-        <v>4237</v>
-      </c>
-      <c r="H16" s="94" t="n">
-        <v>25551</v>
-      </c>
-      <c r="I16" s="94" t="n">
-        <v>39407</v>
-      </c>
-      <c r="J16" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K16" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L16" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M16" s="94" t="inlineStr">
-        <is>
-          <t>PaymentsToAcquirePPE + Capitalized internal-use software (10-K CF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B17" s="94" t="inlineStr">
-        <is>
-          <t>Changes in NWC</t>
-        </is>
-      </c>
-      <c r="C17" s="94" t="inlineStr">
-        <is>
-          <t>3S!row64; DCF!E25</t>
-        </is>
-      </c>
-      <c r="D17" s="94" t="inlineStr">
-        <is>
-          <t>Derived Δ(Accounts receivable − Accounts payable)</t>
-        </is>
-      </c>
-      <c r="E17" s="94" t="inlineStr">
-        <is>
-          <t>Not a single printed 10-K total. Built from BS: AR and AP. CF also shows AR/AP working-capital lines separately.</t>
-        </is>
-      </c>
-      <c r="F17" s="94" t="inlineStr">
-        <is>
-          <t>Balance Sheet + Cash Flow working capital lines</t>
-        </is>
-      </c>
-      <c r="G17" s="94" t="n">
-        <v>63801</v>
-      </c>
-      <c r="H17" s="94" t="n">
-        <v>35231</v>
-      </c>
-      <c r="I17" s="94" t="n">
-        <v>92664</v>
-      </c>
-      <c r="J17" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K17" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L17" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M17" s="94" t="inlineStr">
-        <is>
-          <t>Derived from AccountsReceivableNetCurrent &amp; AccountsPayableCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B18" s="94" t="inlineStr">
-        <is>
-          <t>Operating Cash Flow</t>
-        </is>
-      </c>
-      <c r="C18" s="94" t="inlineStr">
-        <is>
-          <t>3S!row65</t>
-        </is>
-      </c>
-      <c r="D18" s="94" t="inlineStr">
-        <is>
-          <t>Net cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="E18" s="94" t="inlineStr">
-        <is>
-          <t>Same meaning; FICO wording is longer.</t>
-        </is>
-      </c>
-      <c r="F18" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Statements of Cash Flows</t>
-        </is>
-      </c>
-      <c r="G18" s="94" t="n">
-        <v>468915</v>
-      </c>
-      <c r="H18" s="94" t="n">
-        <v>632964</v>
-      </c>
-      <c r="I18" s="94" t="n">
-        <v>778807</v>
-      </c>
-      <c r="J18" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K18" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L18" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M18" s="94" t="inlineStr">
-        <is>
-          <t>NetCashProvidedByUsedInOperatingActivities</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B19" s="94" t="inlineStr">
-        <is>
-          <t>Cash &amp; Equivalents</t>
-        </is>
-      </c>
-      <c r="C19" s="94" t="inlineStr">
-        <is>
-          <t>3S!row41; DCF!D14 (overridden by 10-Q bridge)</t>
-        </is>
-      </c>
-      <c r="D19" s="94" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="E19" s="94" t="inlineStr">
-        <is>
-          <t>YE 10-K cash. DCF bridge may use later 10-Q cash + marketable securities.</t>
-        </is>
-      </c>
-      <c r="F19" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G19" s="94" t="n">
-        <v>136778</v>
-      </c>
-      <c r="H19" s="94" t="n">
-        <v>150667</v>
-      </c>
-      <c r="I19" s="94" t="n">
-        <v>134136</v>
-      </c>
-      <c r="J19" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K19" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L19" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M19" s="94" t="inlineStr">
-        <is>
-          <t>CashAndCashEquivalentsAtCarryingValue</t>
-        </is>
-      </c>
     </row>
     <row r="20">
-      <c r="A20" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B20" s="94" t="inlineStr">
-        <is>
-          <t>Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C20" s="94" t="inlineStr">
-        <is>
-          <t>3S!row42</t>
-        </is>
-      </c>
-      <c r="D20" s="94" t="inlineStr">
-        <is>
-          <t>Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="E20" s="94" t="inlineStr">
-        <is>
-          <t>Same; 10-K says ', net'.</t>
-        </is>
-      </c>
-      <c r="F20" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G20" s="94" t="n">
-        <v>387947</v>
-      </c>
-      <c r="H20" s="94" t="n">
-        <v>426642</v>
-      </c>
-      <c r="I20" s="94" t="n">
-        <v>529148</v>
-      </c>
-      <c r="J20" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K20" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L20" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M20" s="94" t="inlineStr">
-        <is>
-          <t>AccountsReceivableNetCurrent</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UFCF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Capex</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B21" s="94" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="C21" s="94" t="inlineStr">
-        <is>
-          <t>3S!row43</t>
-        </is>
-      </c>
-      <c r="D21" s="94" t="inlineStr">
-        <is>
-          <t>(not material / not presented)</t>
-        </is>
-      </c>
-      <c r="E21" s="94" t="inlineStr">
-        <is>
-          <t>FICO software/scores business — no material inventory line; model uses 0.</t>
-        </is>
-      </c>
-      <c r="F21" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G21" s="94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K21" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L21" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M21" s="94" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+      <c r="A21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1031318</v>
+      </c>
+      <c r="C21" t="n">
+        <v>752304</v>
+      </c>
+      <c r="D21" t="n">
+        <v>42560</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B22" s="94" t="inlineStr">
-        <is>
-          <t>Current Assets</t>
-        </is>
-      </c>
-      <c r="C22" s="94" t="inlineStr">
-        <is>
-          <t>not a CFI hard input (informational)</t>
-        </is>
-      </c>
-      <c r="D22" s="94" t="inlineStr">
-        <is>
-          <t>Total current assets</t>
-        </is>
-      </c>
-      <c r="E22" s="94" t="inlineStr">
-        <is>
-          <t>From 10-K balance sheet total current assets.</t>
-        </is>
-      </c>
-      <c r="F22" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G22" s="94" t="n">
-        <v>556448</v>
-      </c>
-      <c r="H22" s="94" t="n">
-        <v>617413</v>
-      </c>
-      <c r="I22" s="94" t="n">
-        <v>705165</v>
-      </c>
-      <c r="J22" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K22" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L22" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M22" s="94" t="inlineStr">
-        <is>
-          <t>AssetsCurrent</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1149880</v>
+      </c>
+      <c r="C22" t="n">
+        <v>850856</v>
+      </c>
+      <c r="D22" t="n">
+        <v>45964</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B23" s="94" t="inlineStr">
-        <is>
-          <t>Net PP&amp;E</t>
-        </is>
-      </c>
-      <c r="C23" s="94" t="inlineStr">
-        <is>
-          <t>3S!row44</t>
-        </is>
-      </c>
-      <c r="D23" s="94" t="inlineStr">
-        <is>
-          <t>Property and equipment, net</t>
-        </is>
-      </c>
-      <c r="E23" s="94" t="inlineStr">
-        <is>
-          <t>Same meaning.</t>
-        </is>
-      </c>
-      <c r="F23" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G23" s="94" t="n">
-        <v>10966</v>
-      </c>
-      <c r="H23" s="94" t="n">
-        <v>38465</v>
-      </c>
-      <c r="I23" s="94" t="n">
-        <v>67713</v>
-      </c>
-      <c r="J23" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K23" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L23" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M23" s="94" t="inlineStr">
-        <is>
-          <t>PropertyPlantAndEquipmentNet</t>
-        </is>
+      <c r="A23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1270112</v>
+      </c>
+      <c r="C23" t="n">
+        <v>947058</v>
+      </c>
+      <c r="D23" t="n">
+        <v>49641</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B24" s="94" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="C24" s="94" t="inlineStr">
-        <is>
-          <t>3S!row45 (formula in template)</t>
-        </is>
-      </c>
-      <c r="D24" s="94" t="inlineStr">
-        <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="E24" s="94" t="inlineStr">
-        <is>
-          <t>SEC total assets provided for reference; CFI row 45 is a SUM formula — do not overwrite.</t>
-        </is>
-      </c>
-      <c r="F24" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G24" s="94" t="n">
-        <v>1575281</v>
-      </c>
-      <c r="H24" s="94" t="n">
-        <v>1717884</v>
-      </c>
-      <c r="I24" s="94" t="n">
-        <v>1868133</v>
-      </c>
-      <c r="J24" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K24" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L24" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M24" s="94" t="inlineStr">
-        <is>
-          <t>Assets</t>
-        </is>
+      <c r="A24" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1398473</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1050674</v>
+      </c>
+      <c r="D24" t="n">
+        <v>53613</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B25" s="94" t="inlineStr">
-        <is>
-          <t>Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C25" s="94" t="inlineStr">
-        <is>
-          <t>3S!row48</t>
-        </is>
-      </c>
-      <c r="D25" s="94" t="inlineStr">
-        <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="E25" s="94" t="inlineStr">
-        <is>
-          <t>Same naming.</t>
-        </is>
-      </c>
-      <c r="F25" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G25" s="94" t="n">
-        <v>19009</v>
-      </c>
-      <c r="H25" s="94" t="n">
-        <v>22473</v>
-      </c>
-      <c r="I25" s="94" t="n">
-        <v>32315</v>
-      </c>
-      <c r="J25" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K25" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L25" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M25" s="94" t="inlineStr">
-        <is>
-          <t>AccountsPayableCurrent</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement / DCF</t>
-        </is>
-      </c>
-      <c r="B26" s="94" t="inlineStr">
-        <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="C26" s="94" t="inlineStr">
-        <is>
-          <t>3S!row49; DCF!D13 (10-Q override optional)</t>
-        </is>
-      </c>
-      <c r="D26" s="94" t="inlineStr">
-        <is>
-          <t>Current maturities of long-term debt + Long-term debt</t>
-        </is>
-      </c>
-      <c r="E26" s="94" t="inlineStr">
-        <is>
-          <t>Sum of current + noncurrent debt from BS / debt footnote. FY25 total debt 3,055,691. DCF may override D13 with later 10-Q debt.</t>
-        </is>
-      </c>
-      <c r="F26" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets / Debt footnote</t>
-        </is>
-      </c>
-      <c r="G26" s="94" t="n">
-        <v>1811658</v>
-      </c>
-      <c r="H26" s="94" t="n">
-        <v>2209021</v>
-      </c>
-      <c r="I26" s="94" t="n">
-        <v>3055691</v>
-      </c>
-      <c r="J26" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K26" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L26" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M26" s="94" t="inlineStr">
-        <is>
-          <t>LongTermDebtCurrent + LongTermDebtNoncurrent / 10-K note</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
-        </is>
-      </c>
-      <c r="C27" s="94" t="inlineStr">
-        <is>
-          <t>3S!row53</t>
-        </is>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="E27" s="94" t="inlineStr">
-        <is>
-          <t>Same; equity section of balance sheet / equity statement.</t>
-        </is>
-      </c>
-      <c r="F27" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets / Stockholders' equity</t>
-        </is>
-      </c>
-      <c r="G27" s="94" t="n">
-        <v>3388059</v>
-      </c>
-      <c r="H27" s="94" t="n">
-        <v>3900870</v>
-      </c>
-      <c r="I27" s="94" t="n">
-        <v>4552816</v>
-      </c>
-      <c r="J27" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K27" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L27" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M27" s="94" t="inlineStr">
-        <is>
-          <t>RetainedEarningsAccumulatedDeficit</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="94" t="inlineStr">
-        <is>
-          <t>3-Statement</t>
-        </is>
-      </c>
-      <c r="B28" s="94" t="inlineStr">
-        <is>
-          <t>Total Equity</t>
-        </is>
-      </c>
-      <c r="C28" s="94" t="inlineStr">
-        <is>
-          <t>3S!row54 (formula/total)</t>
-        </is>
-      </c>
-      <c r="D28" s="94" t="inlineStr">
-        <is>
-          <t>Total stockholders' deficit / equity</t>
-        </is>
-      </c>
-      <c r="E28" s="94" t="inlineStr">
-        <is>
-          <t>FICO reports stockholders' deficit (negative equity) due to buybacks.</t>
-        </is>
-      </c>
-      <c r="F28" s="94" t="inlineStr">
-        <is>
-          <t>Consolidated Balance Sheets</t>
-        </is>
-      </c>
-      <c r="G28" s="94" t="n">
-        <v>-687990</v>
-      </c>
-      <c r="H28" s="94" t="n">
-        <v>-962679</v>
-      </c>
-      <c r="I28" s="94" t="n">
-        <v>-1745784</v>
-      </c>
-      <c r="J28" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-      <c r="K28" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-      <c r="L28" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-      <c r="M28" s="94" t="inlineStr">
-        <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="92" t="inlineStr">
-        <is>
-          <t>FILING INDEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>FY2025 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B32" s="96" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>FY2024 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B33" s="96" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000162828024045719/fico-20240930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>FY2023 10-K HTML</t>
-        </is>
-      </c>
-      <c r="B34" s="96" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454723000022/fico-20230930.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>SEC companyfacts API</t>
-        </is>
-      </c>
-      <c r="B35" s="96" t="inlineStr">
-        <is>
-          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000814547.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10-Q browse (debt/cash bridge)</t>
-        </is>
-      </c>
-      <c r="B36" s="96" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0000814547&amp;type=10-Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="92" t="inlineStr">
-        <is>
-          <t>DCF bridge overrides (not YE 10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>DCF!D13 Debt (10-Q)</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>5582389</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Later interim debt; override YE 10-K if bridging to current EV</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DCF!D14 Cash (10-Q cash+mkt secs)</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>304537</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Cash &amp; cash equivalents + marketable securities from latest 10-Q bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>DCF!D11 Price / D12 Shares</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1046.23 / 21597.635</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Market price &amp; diluted shares (000s) — not from 10-K income statement</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1533660</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1160650</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57902</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3554,7 +1481,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO — 3 Statement Model (CFI template + 10-K actuals)</t>
+          <t>FICO 3-Statement — corrected forecast drivers</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -3702,7 +1629,7 @@
       <c r="B20" s="85" t="n"/>
       <c r="C20" s="86" t="inlineStr">
         <is>
-          <t>See 10K_Sources sheet for SEC links and naming notes. Columns widened so values are visible.</t>
+          <t>This Excel model is for educational purposes only and should not be used for any other reason.</t>
         </is>
       </c>
       <c r="D20" s="86" t="n"/>
@@ -3923,20 +1850,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
-    <col width="28" customWidth="1" style="19" min="2" max="3"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" style="47" min="4" max="4"/>
-    <col width="18" customWidth="1" style="19" min="5" max="9"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" style="19" min="10" max="14"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" style="19" min="15" max="16384"/>
+    <col width="34" customWidth="1" style="19" min="2" max="3"/>
+    <col width="15.5546875" customWidth="1" style="47" min="4" max="4"/>
+    <col width="15" customWidth="1" style="19" min="5" max="9"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" style="19" min="10" max="14"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" style="19" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3976,44 +1902,35 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="97" t="n">
+      <c r="E2" s="95" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="83">
-        <f>+E2+1</f>
-        <v/>
-      </c>
-      <c r="G2" s="83">
-        <f>+F2+1</f>
-        <v/>
-      </c>
-      <c r="H2" s="83">
-        <f>+G2+1</f>
-        <v/>
-      </c>
-      <c r="I2" s="83">
-        <f>+H2+1</f>
-        <v/>
-      </c>
-      <c r="J2" s="64">
-        <f>+I2+1</f>
-        <v/>
-      </c>
-      <c r="K2" s="64">
-        <f>+J2+1</f>
-        <v/>
-      </c>
-      <c r="L2" s="64">
-        <f>+K2+1</f>
-        <v/>
-      </c>
-      <c r="M2" s="64">
-        <f>+L2+1</f>
-        <v/>
-      </c>
-      <c r="N2" s="64">
-        <f>+M2+1</f>
-        <v/>
+      <c r="F2" s="95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G2" s="95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="95" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I2" s="95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J2" s="96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K2" s="96" t="n">
+        <v>2027</v>
+      </c>
+      <c r="L2" s="96" t="n">
+        <v>2028</v>
+      </c>
+      <c r="M2" s="96" t="n">
+        <v>2029</v>
+      </c>
+      <c r="N2" s="96" t="n">
+        <v>2030</v>
       </c>
     </row>
     <row r="3">
@@ -4116,20 +2033,20 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="67" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K7" s="67" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="L7" s="67" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="M7" s="67" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="N7" s="67" t="n">
-        <v>0.03</v>
+      <c r="J7" s="97" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K7" s="97" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M7" s="97" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N7" s="97" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="8" hidden="1" outlineLevel="1">
@@ -4160,20 +2077,20 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="67" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K8" s="67" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L8" s="67" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M8" s="67" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N8" s="67" t="n">
-        <v>0.35</v>
+      <c r="J8" s="97" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="K8" s="97" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="L8" s="97" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="M8" s="97" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="N8" s="97" t="n">
+        <v>0.1777</v>
       </c>
     </row>
     <row r="9" hidden="1" outlineLevel="1">
@@ -4204,20 +2121,20 @@
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K9" s="33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L9" s="33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M9" s="33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="N9" s="33" t="n">
-        <v>25000</v>
+      <c r="J9" s="98" t="n">
+        <v>574591.4</v>
+      </c>
+      <c r="K9" s="98" t="n">
+        <v>620763.9</v>
+      </c>
+      <c r="L9" s="98" t="n">
+        <v>664386.1</v>
+      </c>
+      <c r="M9" s="98" t="n">
+        <v>697968.9</v>
+      </c>
+      <c r="N9" s="98" t="n">
+        <v>719548.3</v>
       </c>
     </row>
     <row r="10" hidden="1" outlineLevel="1">
@@ -4248,20 +2165,20 @@
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M10" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="N10" s="33" t="n">
-        <v>10000</v>
+      <c r="J10" s="98" t="n">
+        <v>210948.6</v>
+      </c>
+      <c r="K10" s="98" t="n">
+        <v>227899.9</v>
+      </c>
+      <c r="L10" s="98" t="n">
+        <v>243914.8</v>
+      </c>
+      <c r="M10" s="98" t="n">
+        <v>256244</v>
+      </c>
+      <c r="N10" s="98" t="n">
+        <v>264166.4</v>
       </c>
     </row>
     <row r="11" hidden="1" outlineLevel="1">
@@ -4292,20 +2209,20 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K11" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M11" s="67" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N11" s="67" t="n">
-        <v>0.4</v>
+      <c r="J11" s="97" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K11" s="97" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L11" s="97" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M11" s="97" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N11" s="97" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12" hidden="1" outlineLevel="1">
@@ -4336,20 +2253,20 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K12" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L12" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M12" s="67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="N12" s="67" t="n">
-        <v>0.03</v>
+      <c r="J12" s="97" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="K12" s="97" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="L12" s="97" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="M12" s="97" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="N12" s="97" t="n">
+        <v>0.0437</v>
       </c>
     </row>
     <row r="13" hidden="1" outlineLevel="1">
@@ -4380,20 +2297,20 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="67" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K13" s="67" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L13" s="67" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M13" s="67" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="N13" s="67" t="n">
-        <v>0.28</v>
+      <c r="J13" s="97" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="K13" s="97" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="L13" s="97" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="M13" s="97" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="N13" s="97" t="n">
+        <v>0.1877</v>
       </c>
     </row>
     <row r="14" hidden="1" outlineLevel="1">
@@ -4442,20 +2359,20 @@
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="L15" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="M15" s="33" t="n">
-        <v>18</v>
-      </c>
-      <c r="N15" s="33" t="n">
-        <v>18</v>
+      <c r="J15" s="98" t="n">
+        <v>97</v>
+      </c>
+      <c r="K15" s="98" t="n">
+        <v>97</v>
+      </c>
+      <c r="L15" s="98" t="n">
+        <v>97</v>
+      </c>
+      <c r="M15" s="98" t="n">
+        <v>97</v>
+      </c>
+      <c r="N15" s="98" t="n">
+        <v>97</v>
       </c>
     </row>
     <row r="16" hidden="1" outlineLevel="1">
@@ -4485,20 +2402,20 @@
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="33" t="n">
-        <v>73</v>
-      </c>
-      <c r="K16" s="33" t="n">
-        <v>73</v>
-      </c>
-      <c r="L16" s="33" t="n">
-        <v>73</v>
-      </c>
-      <c r="M16" s="33" t="n">
-        <v>73</v>
-      </c>
-      <c r="N16" s="33" t="n">
-        <v>73</v>
+      <c r="J16" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17" hidden="1" outlineLevel="1">
@@ -4528,20 +2445,20 @@
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="K17" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="L17" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="M17" s="33" t="n">
-        <v>37</v>
-      </c>
-      <c r="N17" s="33" t="n">
-        <v>37</v>
+      <c r="J17" s="98" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K17" s="98" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L17" s="98" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="M17" s="98" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="N17" s="98" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="18" hidden="1" outlineLevel="1">
@@ -4570,20 +2487,20 @@
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="33" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K18" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L18" s="33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M18" s="33" t="n">
-        <v>10000</v>
-      </c>
-      <c r="N18" s="33" t="n">
-        <v>15000</v>
+      <c r="J18" s="98" t="n">
+        <v>42559.6</v>
+      </c>
+      <c r="K18" s="98" t="n">
+        <v>45964.3</v>
+      </c>
+      <c r="L18" s="98" t="n">
+        <v>49641.5</v>
+      </c>
+      <c r="M18" s="98" t="n">
+        <v>53612.8</v>
+      </c>
+      <c r="N18" s="98" t="n">
+        <v>57901.8</v>
       </c>
     </row>
     <row r="19" hidden="1" outlineLevel="1">
@@ -4612,19 +2529,19 @@
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="33" t="n">
+      <c r="J19" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="33" t="n">
+      <c r="K19" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="33" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="M19" s="33" t="n">
+      <c r="L19" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="33" t="n">
+      <c r="M19" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4654,19 +2571,19 @@
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="33" t="n">
+      <c r="J20" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="33" t="n">
+      <c r="K20" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="33" t="n">
+      <c r="L20" s="98" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="33" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="N20" s="33" t="n">
+      <c r="M20" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4716,7 +2633,7 @@
     <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Reveneue</t>
+          <t>Revenue (FICO: Revenues)</t>
         </is>
       </c>
       <c r="C24" s="18" t="n"/>
@@ -4760,7 +2677,7 @@
     <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>Cost of Goods Sold (COGS)</t>
+          <t>COGS (FICO: Cost of revenues)</t>
         </is>
       </c>
       <c r="C25" s="19" t="n"/>
@@ -4872,7 +2789,7 @@
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>Salaries and Benefits</t>
+          <t>SG&amp;A (CFI Salaries ← FICO SG&amp;A)</t>
         </is>
       </c>
       <c r="E28" s="98" t="n">
@@ -4914,7 +2831,7 @@
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>Rent and Overhead</t>
+          <t>R&amp;D (CFI Rent/Overhead ← FICO R&amp;D)</t>
         </is>
       </c>
       <c r="E29" s="98" t="n">
@@ -7556,7 +5473,7 @@
     <row r="131">
       <c r="B131" s="101" t="inlineStr">
         <is>
-          <t>FICO 10-K sources: see sheet '10K_Sources' and FICO/DCF_FICO_SOURCES.csv</t>
+          <t>FIXED: forecast drivers now FICO-scale (COGS%~17.8%, SG&amp;A/R&amp;D from FY25, tax~18.8%, AR days~97, Inv days=0, Capex from 10-K). Years 2021–2030 hardcoded.</t>
         </is>
       </c>
     </row>

--- a/FICO/3S_FICO.xlsx
+++ b/FICO/3S_FICO.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22296" windowHeight="8376" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Audit_Fixes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Formula_Map" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="3 Statement Model" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
@@ -284,7 +284,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -313,11 +313,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -391,7 +386,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -539,14 +534,17 @@
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="1" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="1" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="166" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="10" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="26" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -601,7 +599,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>FICO Revenue FY2021–2030</a:t>
+              <a:t>Revenue (formula forecast J24:N24)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -966,349 +964,554 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="92" t="inlineStr">
         <is>
-          <t>Errors found and fixed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="93" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B3" s="93" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="C3" s="93" t="inlineStr">
-        <is>
-          <t>Fix</t>
+          <t>Updated math — Excel formula dependencies (not typed results)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yellow cells = inputs. Green/white formula cells = depend on other rows/sheets.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3S forecast COGS%</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Was 37% (CFI sample)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Now 17.77% from FY25</t>
+      <c r="A4" s="93" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B4" s="93" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="C4" s="93" t="inlineStr">
+        <is>
+          <t>Excel formula / dependency</t>
+        </is>
+      </c>
+      <c r="D4" s="93" t="inlineStr">
+        <is>
+          <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3S forecast SG&amp;A/R&amp;D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Was $25k / $10k</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Now FY25 SG&amp;A/R&amp;D grown with revenue</t>
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B5" s="94" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C5" s="94" t="inlineStr">
+        <is>
+          <t>input (or ='03_Three_Statement'!J13 if joined)</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>FY25 ETR</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3S forecast tax</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Was 28%</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Now 18.77% FY25 ETR</t>
+      <c r="A6" s="94" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
+      <c r="B6" s="94" t="inlineStr">
+        <is>
+          <t>E17:I17</t>
+        </is>
+      </c>
+      <c r="C6" s="94">
+        <f>YEAR(E18) …</f>
+        <v/>
+      </c>
+      <c r="D6" s="94" t="inlineStr">
+        <is>
+          <t>Depends on date row</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3S AR / Inv days</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Was 18 / 73</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Now ~97 / 0</t>
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t>Dates</t>
+        </is>
+      </c>
+      <c r="B7" s="94" t="inlineStr">
+        <is>
+          <t>E18:I18</t>
+        </is>
+      </c>
+      <c r="C7" s="94">
+        <f>DATE(YEAR($D$10)+E19,9,30)</f>
+        <v/>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>Depends on FYE + period</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3S Capex forecast</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Was ~15k sample</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Now from FY25 39,407 growing 8%/yr</t>
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>Periods</t>
+        </is>
+      </c>
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>F19:I19</t>
+        </is>
+      </c>
+      <c r="C8" s="94">
+        <f>E19+1 …</f>
+        <v/>
+      </c>
+      <c r="D8" s="94" t="inlineStr">
+        <is>
+          <t>Depends on prior period</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>3S year headers</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Formulas blank pre-calc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Hardcoded 2021–2030</t>
+      <c r="A9" s="94" t="inlineStr">
+        <is>
+          <t>Year fraction</t>
+        </is>
+      </c>
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>E20:I20</t>
+        </is>
+      </c>
+      <c r="C9" s="94">
+        <f>YEARFRAC(prior_date, date)</f>
+        <v/>
+      </c>
+      <c r="D9" s="94" t="inlineStr">
+        <is>
+          <t>Discount stub</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DCF Year-1 EBIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Started ~1,048,623 (&gt;FY25 OpInc)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Path anchored to FY25 OpInc 924,850</t>
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B10" s="94" t="inlineStr">
+        <is>
+          <t>E21:I21</t>
+        </is>
+      </c>
+      <c r="C10" s="94" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$3*(1+E4) then rolls; Joined: 3-stmt GP−opex−DA</t>
+        </is>
+      </c>
+      <c r="D10" s="94" t="inlineStr">
+        <is>
+          <t>Operating income path</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DCF D&amp;A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Used ~18k (0.8% rev)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Anchored to FY25 D&amp;A 14,952</t>
+      <c r="A11" s="94" t="inlineStr">
+        <is>
+          <t>Cash Taxes</t>
+        </is>
+      </c>
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>E22:I22</t>
+        </is>
+      </c>
+      <c r="C11" s="94">
+        <f>E21*$D$5</f>
+        <v/>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>Depends on EBIT and tax rate</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DCF years</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Unclear / missing FY25 base</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>FY25 actuals in row 16; forecast 2026–2030</t>
+      <c r="A12" s="94" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B12" s="94" t="inlineStr">
+        <is>
+          <t>E23:I23</t>
+        </is>
+      </c>
+      <c r="C12" s="94" t="inlineStr">
+        <is>
+          <t>Standalone: =$E$3*E21/$D$3; Joined: ='03_Three_Statement'!J30</t>
+        </is>
+      </c>
+      <c r="D12" s="94" t="inlineStr">
+        <is>
+          <t>Depends on EBIT or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DCF Capex</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Flat 39,407</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Grows 8%/yr with investment</t>
+      <c r="A13" s="94" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B13" s="94" t="inlineStr">
+        <is>
+          <t>E24:I24</t>
+        </is>
+      </c>
+      <c r="C13" s="94" t="inlineStr">
+        <is>
+          <t>Standalone: =$D$15*(1+$D$16)^E19; Joined: 3-stmt!J68</t>
+        </is>
+      </c>
+      <c r="D13" s="94" t="inlineStr">
+        <is>
+          <t>Depends on base capex/growth or 3-stmt</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DCF EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>25x → huge TV vs PG</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Set 22x; still show PG / multiple / average</t>
+      <c r="A14" s="94" t="inlineStr">
+        <is>
+          <t>ΔNWC</t>
+        </is>
+      </c>
+      <c r="B14" s="94" t="inlineStr">
+        <is>
+          <t>E25:I25</t>
+        </is>
+      </c>
+      <c r="C14" s="94" t="inlineStr">
+        <is>
+          <t>Standalone: =MAX(0,ΔEBIT)*5%; Joined: 3-stmt!J89</t>
+        </is>
+      </c>
+      <c r="D14" s="94" t="inlineStr">
+        <is>
+          <t>WC investment</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DCF blanks</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Taxes/Capex/UFCF/TV formulas blank in viewer</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Written as computed values + chart</t>
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>Unlevered FCF</t>
+        </is>
+      </c>
+      <c r="B15" s="94" t="inlineStr">
+        <is>
+          <t>E26:I26</t>
+        </is>
+      </c>
+      <c r="C15" s="94">
+        <f>EBIT − Tax + D&amp;A − Capex − ΔNWC</f>
+        <v/>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>Core FCF identity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="94" t="inlineStr">
+        <is>
+          <t>TV (PG)</t>
+        </is>
+      </c>
+      <c r="B16" s="94" t="inlineStr">
+        <is>
+          <t>N18</t>
+        </is>
+      </c>
+      <c r="C16" s="94">
+        <f>(I26*(1+D7))/(D6-D7)</f>
+        <v/>
+      </c>
+      <c r="D16" s="94" t="inlineStr">
+        <is>
+          <t>Gordon growth on final UFCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>TV (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="B17" s="94" t="inlineStr">
+        <is>
+          <t>N19</t>
+        </is>
+      </c>
+      <c r="C17" s="94">
+        <f>D8*(I21+I23)</f>
+        <v/>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>Exit multiple on final EBITDA</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K</t>
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>TV Average</t>
         </is>
       </c>
       <c r="B18" s="94" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="C18" s="94">
+        <f>AVERAGE(N18:N19)</f>
+        <v/>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>Blended exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="94" t="inlineStr">
+        <is>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B19" s="94" t="inlineStr">
+        <is>
+          <t>D32</t>
+        </is>
+      </c>
+      <c r="C19" s="94">
+        <f>XNPV(D6,D28:J28,D18:J18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>PV of transaction CFs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="94" t="inlineStr">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B20" s="94" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="C20" s="94">
+        <f>D32+D33−D34</f>
+        <v/>
+      </c>
+      <c r="D20" s="94" t="inlineStr">
+        <is>
+          <t>EV + cash − debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>Equity / share</t>
+        </is>
+      </c>
+      <c r="B21" s="94" t="inlineStr">
+        <is>
+          <t>D37</t>
+        </is>
+      </c>
+      <c r="C21" s="94">
+        <f>D35/D12</f>
+        <v/>
+      </c>
+      <c r="D21" s="94" t="inlineStr">
+        <is>
+          <t>Depends on equity &amp; shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>3S Revenue fcst</t>
+        </is>
+      </c>
+      <c r="B22" s="94" t="inlineStr">
+        <is>
+          <t>J24</t>
+        </is>
+      </c>
+      <c r="C22" s="94">
+        <f>I24*(1+J7)</f>
+        <v/>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>Grows from prior year</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="94" t="inlineStr">
+        <is>
+          <t>3S COGS fcst</t>
+        </is>
+      </c>
+      <c r="B23" s="94" t="inlineStr">
+        <is>
+          <t>J25</t>
+        </is>
+      </c>
+      <c r="C23" s="94">
+        <f>J24*J8</f>
+        <v/>
+      </c>
+      <c r="D23" s="94" t="inlineStr">
+        <is>
+          <t>Depends on revenue &amp; COGS%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>3S Gross Profit</t>
+        </is>
+      </c>
+      <c r="B24" s="94" t="inlineStr">
+        <is>
+          <t>J26</t>
+        </is>
+      </c>
+      <c r="C24" s="94">
+        <f>J24-J25</f>
+        <v/>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>Depends on Rev &amp; COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="94" t="inlineStr">
+        <is>
+          <t>3S SG&amp;A fcst</t>
+        </is>
+      </c>
+      <c r="B25" s="94" t="inlineStr">
+        <is>
+          <t>J28</t>
+        </is>
+      </c>
+      <c r="C25" s="94">
+        <f>J9</f>
+        <v/>
+      </c>
+      <c r="D25" s="94" t="inlineStr">
+        <is>
+          <t>Depends on salaries driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="94" t="inlineStr">
+        <is>
+          <t>3S Capex fcst</t>
+        </is>
+      </c>
+      <c r="B26" s="94" t="inlineStr">
+        <is>
+          <t>J68</t>
+        </is>
+      </c>
+      <c r="C26" s="94">
+        <f>J18</f>
+        <v/>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
+        <is>
+          <t>Depends on capex assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>3S ΔNWC fcst</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>J89</t>
+        </is>
+      </c>
+      <c r="C27" s="94">
+        <f>J88-I88</f>
+        <v/>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>Depends on NWC schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="B30" s="95" t="inlineStr">
+        <is>
           <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>UFCF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B21" t="n">
-        <v>1031318</v>
-      </c>
-      <c r="C21" t="n">
-        <v>752304</v>
-      </c>
-      <c r="D21" t="n">
-        <v>42560</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1149880</v>
-      </c>
-      <c r="C22" t="n">
-        <v>850856</v>
-      </c>
-      <c r="D22" t="n">
-        <v>45964</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B23" t="n">
-        <v>1270112</v>
-      </c>
-      <c r="C23" t="n">
-        <v>947058</v>
-      </c>
-      <c r="D23" t="n">
-        <v>49641</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B24" t="n">
-        <v>1398473</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1050674</v>
-      </c>
-      <c r="D24" t="n">
-        <v>53613</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B25" t="n">
-        <v>1533660</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1160650</v>
-      </c>
-      <c r="D25" t="n">
-        <v>57902</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1481,7 +1684,7 @@
       <c r="B12" s="74" t="n"/>
       <c r="C12" s="75" t="inlineStr">
         <is>
-          <t>FICO 3-Statement — corrected forecast drivers</t>
+          <t>3 Statement Model</t>
         </is>
       </c>
       <c r="D12" s="74" t="n"/>
@@ -1850,7 +2053,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="15.6" outlineLevelRow="1"/>
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
-    <col width="34" customWidth="1" style="19" min="2" max="3"/>
+    <col width="36" customWidth="1" style="19" min="2" max="3"/>
     <col width="15.5546875" customWidth="1" style="47" min="4" max="4"/>
     <col width="15" customWidth="1" style="19" min="5" max="9"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -1902,35 +2105,44 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="95" t="n">
+      <c r="E2" s="96" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="95" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G2" s="95" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H2" s="95" t="n">
-        <v>2024</v>
-      </c>
-      <c r="I2" s="95" t="n">
-        <v>2025</v>
-      </c>
-      <c r="J2" s="96" t="n">
-        <v>2026</v>
-      </c>
-      <c r="K2" s="96" t="n">
-        <v>2027</v>
-      </c>
-      <c r="L2" s="96" t="n">
-        <v>2028</v>
-      </c>
-      <c r="M2" s="96" t="n">
-        <v>2029</v>
-      </c>
-      <c r="N2" s="96" t="n">
-        <v>2030</v>
+      <c r="F2" s="83">
+        <f>+E2+1</f>
+        <v/>
+      </c>
+      <c r="G2" s="83">
+        <f>+F2+1</f>
+        <v/>
+      </c>
+      <c r="H2" s="83">
+        <f>+G2+1</f>
+        <v/>
+      </c>
+      <c r="I2" s="83">
+        <f>+H2+1</f>
+        <v/>
+      </c>
+      <c r="J2" s="64">
+        <f>+I2+1</f>
+        <v/>
+      </c>
+      <c r="K2" s="64">
+        <f>+J2+1</f>
+        <v/>
+      </c>
+      <c r="L2" s="64">
+        <f>+K2+1</f>
+        <v/>
+      </c>
+      <c r="M2" s="64">
+        <f>+L2+1</f>
+        <v/>
+      </c>
+      <c r="N2" s="64">
+        <f>+M2+1</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -2077,19 +2289,19 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="97" t="n">
+      <c r="J8" s="98" t="n">
         <v>0.1777</v>
       </c>
-      <c r="K8" s="97" t="n">
+      <c r="K8" s="98" t="n">
         <v>0.1777</v>
       </c>
-      <c r="L8" s="97" t="n">
+      <c r="L8" s="98" t="n">
         <v>0.1777</v>
       </c>
-      <c r="M8" s="97" t="n">
+      <c r="M8" s="98" t="n">
         <v>0.1777</v>
       </c>
-      <c r="N8" s="97" t="n">
+      <c r="N8" s="98" t="n">
         <v>0.1777</v>
       </c>
     </row>
@@ -2121,19 +2333,19 @@
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="98" t="n">
+      <c r="J9" s="99" t="n">
         <v>574591.4</v>
       </c>
-      <c r="K9" s="98" t="n">
+      <c r="K9" s="99" t="n">
         <v>620763.9</v>
       </c>
-      <c r="L9" s="98" t="n">
+      <c r="L9" s="99" t="n">
         <v>664386.1</v>
       </c>
-      <c r="M9" s="98" t="n">
+      <c r="M9" s="99" t="n">
         <v>697968.9</v>
       </c>
-      <c r="N9" s="98" t="n">
+      <c r="N9" s="99" t="n">
         <v>719548.3</v>
       </c>
     </row>
@@ -2165,19 +2377,19 @@
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="98" t="n">
+      <c r="J10" s="99" t="n">
         <v>210948.6</v>
       </c>
-      <c r="K10" s="98" t="n">
+      <c r="K10" s="99" t="n">
         <v>227899.9</v>
       </c>
-      <c r="L10" s="98" t="n">
+      <c r="L10" s="99" t="n">
         <v>243914.8</v>
       </c>
-      <c r="M10" s="98" t="n">
+      <c r="M10" s="99" t="n">
         <v>256244</v>
       </c>
-      <c r="N10" s="98" t="n">
+      <c r="N10" s="99" t="n">
         <v>264166.4</v>
       </c>
     </row>
@@ -2209,19 +2421,19 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="97" t="n">
+      <c r="J11" s="98" t="n">
         <v>0.35</v>
       </c>
-      <c r="K11" s="97" t="n">
+      <c r="K11" s="98" t="n">
         <v>0.35</v>
       </c>
-      <c r="L11" s="97" t="n">
+      <c r="L11" s="98" t="n">
         <v>0.35</v>
       </c>
-      <c r="M11" s="97" t="n">
+      <c r="M11" s="98" t="n">
         <v>0.35</v>
       </c>
-      <c r="N11" s="97" t="n">
+      <c r="N11" s="98" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -2253,19 +2465,19 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="97" t="n">
+      <c r="J12" s="98" t="n">
         <v>0.0437</v>
       </c>
-      <c r="K12" s="97" t="n">
+      <c r="K12" s="98" t="n">
         <v>0.0437</v>
       </c>
-      <c r="L12" s="97" t="n">
+      <c r="L12" s="98" t="n">
         <v>0.0437</v>
       </c>
-      <c r="M12" s="97" t="n">
+      <c r="M12" s="98" t="n">
         <v>0.0437</v>
       </c>
-      <c r="N12" s="97" t="n">
+      <c r="N12" s="98" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -2297,19 +2509,19 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="97" t="n">
+      <c r="J13" s="98" t="n">
         <v>0.1877</v>
       </c>
-      <c r="K13" s="97" t="n">
+      <c r="K13" s="98" t="n">
         <v>0.1877</v>
       </c>
-      <c r="L13" s="97" t="n">
+      <c r="L13" s="98" t="n">
         <v>0.1877</v>
       </c>
-      <c r="M13" s="97" t="n">
+      <c r="M13" s="98" t="n">
         <v>0.1877</v>
       </c>
-      <c r="N13" s="97" t="n">
+      <c r="N13" s="98" t="n">
         <v>0.1877</v>
       </c>
     </row>
@@ -2359,19 +2571,19 @@
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="98" t="n">
+      <c r="J15" s="99" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="98" t="n">
+      <c r="K15" s="99" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="98" t="n">
+      <c r="L15" s="99" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="98" t="n">
+      <c r="M15" s="99" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="98" t="n">
+      <c r="N15" s="99" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2402,19 +2614,19 @@
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="98" t="n">
+      <c r="J16" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="98" t="n">
+      <c r="K16" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="98" t="n">
+      <c r="L16" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="98" t="n">
+      <c r="M16" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="98" t="n">
+      <c r="N16" s="99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2445,19 +2657,19 @@
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="98" t="n">
+      <c r="J17" s="99" t="n">
         <v>33.3</v>
       </c>
-      <c r="K17" s="98" t="n">
+      <c r="K17" s="99" t="n">
         <v>33.3</v>
       </c>
-      <c r="L17" s="98" t="n">
+      <c r="L17" s="99" t="n">
         <v>33.3</v>
       </c>
-      <c r="M17" s="98" t="n">
+      <c r="M17" s="99" t="n">
         <v>33.3</v>
       </c>
-      <c r="N17" s="98" t="n">
+      <c r="N17" s="99" t="n">
         <v>33.3</v>
       </c>
     </row>
@@ -2487,19 +2699,19 @@
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="98" t="n">
+      <c r="J18" s="99" t="n">
         <v>42559.6</v>
       </c>
-      <c r="K18" s="98" t="n">
+      <c r="K18" s="99" t="n">
         <v>45964.3</v>
       </c>
-      <c r="L18" s="98" t="n">
+      <c r="L18" s="99" t="n">
         <v>49641.5</v>
       </c>
-      <c r="M18" s="98" t="n">
+      <c r="M18" s="99" t="n">
         <v>53612.8</v>
       </c>
-      <c r="N18" s="98" t="n">
+      <c r="N18" s="99" t="n">
         <v>57901.8</v>
       </c>
     </row>
@@ -2529,19 +2741,19 @@
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="98" t="n">
+      <c r="J19" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="98" t="n">
+      <c r="K19" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="98" t="n">
+      <c r="L19" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="98" t="n">
+      <c r="M19" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="98" t="n">
+      <c r="N19" s="99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2571,19 +2783,19 @@
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="98" t="n">
+      <c r="J20" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="98" t="n">
+      <c r="K20" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="98" t="n">
+      <c r="L20" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="98" t="n">
+      <c r="M20" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="98" t="n">
+      <c r="N20" s="99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2638,19 +2850,19 @@
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="98" t="n">
+      <c r="E24" s="99" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="98" t="n">
+      <c r="F24" s="99" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="98" t="n">
+      <c r="G24" s="99" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="98" t="n">
+      <c r="H24" s="99" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="98" t="n">
+      <c r="I24" s="99" t="n">
         <v>1990869</v>
       </c>
       <c r="J24" s="18">
@@ -2682,19 +2894,19 @@
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="98" t="n">
+      <c r="E25" s="99" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="98" t="n">
+      <c r="F25" s="99" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="98" t="n">
+      <c r="G25" s="99" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="98" t="n">
+      <c r="H25" s="99" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="98" t="n">
+      <c r="I25" s="99" t="n">
         <v>353722</v>
       </c>
       <c r="J25" s="55">
@@ -2789,22 +3001,22 @@
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>SG&amp;A (CFI Salaries ← FICO SG&amp;A)</t>
-        </is>
-      </c>
-      <c r="E28" s="98" t="n">
+          <t>SG&amp;A ← Salaries (depends on row 9)</t>
+        </is>
+      </c>
+      <c r="E28" s="99" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="98" t="n">
+      <c r="F28" s="99" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="98" t="n">
+      <c r="G28" s="99" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="98" t="n">
+      <c r="H28" s="99" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="98" t="n">
+      <c r="I28" s="99" t="n">
         <v>513028</v>
       </c>
       <c r="J28" s="19">
@@ -2831,22 +3043,22 @@
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>R&amp;D (CFI Rent/Overhead ← FICO R&amp;D)</t>
-        </is>
-      </c>
-      <c r="E29" s="98" t="n">
+          <t>R&amp;D ← Rent/Overhead (depends on row 10)</t>
+        </is>
+      </c>
+      <c r="E29" s="99" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="98" t="n">
+      <c r="F29" s="99" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="98" t="n">
+      <c r="G29" s="99" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="98" t="n">
+      <c r="H29" s="99" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="98" t="n">
+      <c r="I29" s="99" t="n">
         <v>188347</v>
       </c>
       <c r="J29" s="19">
@@ -2876,19 +3088,19 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="98" t="n">
+      <c r="E30" s="99" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="98" t="n">
+      <c r="F30" s="99" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="98" t="n">
+      <c r="G30" s="99" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="98" t="n">
+      <c r="H30" s="99" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="98" t="n">
+      <c r="I30" s="99" t="n">
         <v>14952</v>
       </c>
       <c r="J30" s="19">
@@ -2920,19 +3132,19 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="99" t="n">
+      <c r="E31" s="100" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="99" t="n">
+      <c r="F31" s="100" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="99" t="n">
+      <c r="G31" s="100" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="99" t="n">
+      <c r="H31" s="100" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="99" t="n">
+      <c r="I31" s="100" t="n">
         <v>133647</v>
       </c>
       <c r="J31" s="16">
@@ -3077,19 +3289,19 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="98" t="n">
+      <c r="E35" s="99" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="98" t="n">
+      <c r="F35" s="99" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="98" t="n">
+      <c r="G35" s="99" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="98" t="n">
+      <c r="H35" s="99" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="98" t="n">
+      <c r="I35" s="99" t="n">
         <v>150649</v>
       </c>
       <c r="J35" s="55">
@@ -3218,19 +3430,19 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="98" t="n">
+      <c r="E41" s="99" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="98" t="n">
+      <c r="F41" s="99" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="98" t="n">
+      <c r="G41" s="99" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="98" t="n">
+      <c r="H41" s="99" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="98" t="n">
+      <c r="I41" s="99" t="n">
         <v>134136</v>
       </c>
       <c r="J41" s="19">
@@ -3260,19 +3472,19 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="98" t="n">
+      <c r="E42" s="99" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="98" t="n">
+      <c r="F42" s="99" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="98" t="n">
+      <c r="G42" s="99" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="98" t="n">
+      <c r="H42" s="99" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="98" t="n">
+      <c r="I42" s="99" t="n">
         <v>529148</v>
       </c>
       <c r="J42" s="42">
@@ -3302,19 +3514,19 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="98" t="n">
+      <c r="E43" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="98" t="n">
+      <c r="F43" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="98" t="n">
+      <c r="G43" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="98" t="n">
+      <c r="H43" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="98" t="n">
+      <c r="I43" s="99" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="19">
@@ -3344,19 +3556,19 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="98" t="n">
+      <c r="E44" s="99" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="98" t="n">
+      <c r="F44" s="99" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="98" t="n">
+      <c r="G44" s="99" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="98" t="n">
+      <c r="H44" s="99" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="98" t="n">
+      <c r="I44" s="99" t="n">
         <v>67713</v>
       </c>
       <c r="J44" s="19">
@@ -3462,19 +3674,19 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="98" t="n">
+      <c r="E48" s="99" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="98" t="n">
+      <c r="F48" s="99" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="98" t="n">
+      <c r="G48" s="99" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="98" t="n">
+      <c r="H48" s="99" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="98" t="n">
+      <c r="I48" s="99" t="n">
         <v>32315</v>
       </c>
       <c r="J48" s="19">
@@ -3504,19 +3716,19 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="98" t="n">
+      <c r="E49" s="99" t="n">
         <v>1009018</v>
       </c>
-      <c r="F49" s="98" t="n">
+      <c r="F49" s="99" t="n">
         <v>1823669</v>
       </c>
-      <c r="G49" s="98" t="n">
+      <c r="G49" s="99" t="n">
         <v>1811658</v>
       </c>
-      <c r="H49" s="98" t="n">
+      <c r="H49" s="99" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="98" t="n">
+      <c r="I49" s="99" t="n">
         <v>3055691</v>
       </c>
       <c r="J49" s="19">
@@ -3607,19 +3819,19 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="98" t="n">
+      <c r="E52" s="99" t="n">
         <v>-3079536</v>
       </c>
-      <c r="F52" s="98" t="n">
+      <c r="F52" s="99" t="n">
         <v>-4326434</v>
       </c>
-      <c r="G52" s="98" t="n">
+      <c r="G52" s="99" t="n">
         <v>-4683035</v>
       </c>
-      <c r="H52" s="98" t="n">
+      <c r="H52" s="99" t="n">
         <v>-5516590</v>
       </c>
-      <c r="I52" s="98" t="n">
+      <c r="I52" s="99" t="n">
         <v>-6909825</v>
       </c>
       <c r="J52" s="19">
@@ -3649,19 +3861,19 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="98" t="n">
+      <c r="E53" s="99" t="n">
         <v>2585143</v>
       </c>
-      <c r="F53" s="98" t="n">
+      <c r="F53" s="99" t="n">
         <v>2958684</v>
       </c>
-      <c r="G53" s="98" t="n">
+      <c r="G53" s="99" t="n">
         <v>3388059</v>
       </c>
-      <c r="H53" s="98" t="n">
+      <c r="H53" s="99" t="n">
         <v>3900870</v>
       </c>
-      <c r="I53" s="98" t="n">
+      <c r="I53" s="99" t="n">
         <v>4552816</v>
       </c>
       <c r="J53" s="19">
@@ -3997,19 +4209,19 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="98" t="n">
+      <c r="E64" s="99" t="n">
         <v>-19789</v>
       </c>
-      <c r="F64" s="98" t="n">
+      <c r="F64" s="99" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="98" t="n">
+      <c r="G64" s="99" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="98" t="n">
+      <c r="H64" s="99" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="98" t="n">
+      <c r="I64" s="99" t="n">
         <v>92664</v>
       </c>
       <c r="J64" s="19">
@@ -4120,19 +4332,19 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="98" t="n">
+      <c r="E68" s="99" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="98" t="n">
+      <c r="F68" s="99" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="98" t="n">
+      <c r="G68" s="99" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="98" t="n">
+      <c r="H68" s="99" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="98" t="n">
+      <c r="I68" s="99" t="n">
         <v>39407</v>
       </c>
       <c r="J68" s="19">
@@ -4243,19 +4455,19 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="98" t="n">
+      <c r="E72" s="99" t="n">
         <v>269583</v>
       </c>
-      <c r="F72" s="98" t="n">
+      <c r="F72" s="99" t="n">
         <v>814651</v>
       </c>
-      <c r="G72" s="98" t="n">
+      <c r="G72" s="99" t="n">
         <v>-12011</v>
       </c>
-      <c r="H72" s="98" t="n">
+      <c r="H72" s="99" t="n">
         <v>397363</v>
       </c>
-      <c r="I72" s="98" t="n">
+      <c r="I72" s="99" t="n">
         <v>846670</v>
       </c>
       <c r="J72" s="19">
@@ -4285,19 +4497,19 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="98" t="n">
+      <c r="E73" s="99" t="n">
         <v>-661519</v>
       </c>
-      <c r="F73" s="98" t="n">
+      <c r="F73" s="99" t="n">
         <v>-1251001</v>
       </c>
-      <c r="G73" s="98" t="n">
+      <c r="G73" s="99" t="n">
         <v>-360388</v>
       </c>
-      <c r="H73" s="98" t="n">
+      <c r="H73" s="99" t="n">
         <v>-849330</v>
       </c>
-      <c r="I73" s="98" t="n">
+      <c r="I73" s="99" t="n">
         <v>-1398028</v>
       </c>
       <c r="J73" s="19">
@@ -4442,16 +4654,16 @@
         <f>D78</f>
         <v/>
       </c>
-      <c r="F77" s="98" t="n">
+      <c r="F77" s="99" t="n">
         <v>195354</v>
       </c>
-      <c r="G77" s="98" t="n">
+      <c r="G77" s="99" t="n">
         <v>133202</v>
       </c>
-      <c r="H77" s="98" t="n">
+      <c r="H77" s="99" t="n">
         <v>136778</v>
       </c>
-      <c r="I77" s="98" t="n">
+      <c r="I77" s="99" t="n">
         <v>150667</v>
       </c>
       <c r="J77" s="19">
@@ -4482,7 +4694,7 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="100" t="n">
+      <c r="D78" s="101" t="n">
         <v>157394</v>
       </c>
       <c r="E78" s="17">
@@ -4634,19 +4846,19 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="98" t="n">
+      <c r="E85" s="99" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="98" t="n">
+      <c r="F85" s="99" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="98" t="n">
+      <c r="G85" s="99" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="98" t="n">
+      <c r="H85" s="99" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="98" t="n">
+      <c r="I85" s="99" t="n">
         <v>529148</v>
       </c>
       <c r="J85" s="19">
@@ -4676,19 +4888,19 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="98" t="n">
+      <c r="E86" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="98" t="n">
+      <c r="F86" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="98" t="n">
+      <c r="G86" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="98" t="n">
+      <c r="H86" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="98" t="n">
+      <c r="I86" s="99" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="19">
@@ -4718,19 +4930,19 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="98" t="n">
+      <c r="E87" s="99" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="98" t="n">
+      <c r="F87" s="99" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="98" t="n">
+      <c r="G87" s="99" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="98" t="n">
+      <c r="H87" s="99" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="98" t="n">
+      <c r="I87" s="99" t="n">
         <v>32315</v>
       </c>
       <c r="J87" s="19">
@@ -4875,19 +5087,19 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="98" t="n">
+      <c r="E92" s="99" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="98" t="n">
+      <c r="F92" s="99" t="n">
         <v>27913</v>
       </c>
-      <c r="G92" s="98" t="n">
+      <c r="G92" s="99" t="n">
         <v>17580</v>
       </c>
-      <c r="H92" s="98" t="n">
+      <c r="H92" s="99" t="n">
         <v>10966</v>
       </c>
-      <c r="I92" s="98" t="n">
+      <c r="I92" s="99" t="n">
         <v>38465</v>
       </c>
       <c r="J92" s="19">
@@ -4917,19 +5129,19 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="98" t="n">
+      <c r="E93" s="99" t="n">
         <v>7086</v>
       </c>
-      <c r="F93" s="98" t="n">
+      <c r="F93" s="99" t="n">
         <v>10132</v>
       </c>
-      <c r="G93" s="98" t="n">
+      <c r="G93" s="99" t="n">
         <v>8024</v>
       </c>
-      <c r="H93" s="98" t="n">
+      <c r="H93" s="99" t="n">
         <v>41326</v>
       </c>
-      <c r="I93" s="98" t="n">
+      <c r="I93" s="99" t="n">
         <v>44200</v>
       </c>
       <c r="J93" s="19">
@@ -4959,19 +5171,19 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="98" t="n">
+      <c r="E94" s="99" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="98" t="n">
+      <c r="F94" s="99" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="98" t="n">
+      <c r="G94" s="99" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="98" t="n">
+      <c r="H94" s="99" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="98" t="n">
+      <c r="I94" s="99" t="n">
         <v>14952</v>
       </c>
       <c r="J94" s="55">
@@ -5074,19 +5286,19 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="98" t="n">
+      <c r="E98" s="99" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="98" t="n">
+      <c r="F98" s="99" t="n">
         <v>1009018</v>
       </c>
-      <c r="G98" s="98" t="n">
+      <c r="G98" s="99" t="n">
         <v>1823669</v>
       </c>
-      <c r="H98" s="98" t="n">
+      <c r="H98" s="99" t="n">
         <v>1811658</v>
       </c>
-      <c r="I98" s="98" t="n">
+      <c r="I98" s="99" t="n">
         <v>2209021</v>
       </c>
       <c r="J98" s="19">
@@ -5116,19 +5328,19 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="98" t="n">
+      <c r="E99" s="99" t="n">
         <v>269583</v>
       </c>
-      <c r="F99" s="98" t="n">
+      <c r="F99" s="99" t="n">
         <v>814651</v>
       </c>
-      <c r="G99" s="98" t="n">
+      <c r="G99" s="99" t="n">
         <v>-12011</v>
       </c>
-      <c r="H99" s="98" t="n">
+      <c r="H99" s="99" t="n">
         <v>397363</v>
       </c>
-      <c r="I99" s="98" t="n">
+      <c r="I99" s="99" t="n">
         <v>846670</v>
       </c>
       <c r="J99" s="52">
@@ -5207,19 +5419,19 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="98" t="n">
+      <c r="E101" s="99" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="98" t="n">
+      <c r="F101" s="99" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="98" t="n">
+      <c r="G101" s="99" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="98" t="n">
+      <c r="H101" s="99" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="98" t="n">
+      <c r="I101" s="99" t="n">
         <v>133647</v>
       </c>
       <c r="J101" s="19">
@@ -5471,9 +5683,9 @@
     <row r="128" hidden="1" outlineLevel="1"/>
     <row r="129" collapsed="1"/>
     <row r="131">
-      <c r="B131" s="101" t="inlineStr">
-        <is>
-          <t>FIXED: forecast drivers now FICO-scale (COGS%~17.8%, SG&amp;A/R&amp;D from FY25, tax~18.8%, AR days~97, Inv days=0, Capex from 10-K). Years 2021–2030 hardcoded.</t>
+      <c r="B131" s="102" t="inlineStr">
+        <is>
+          <t>Yellow = inputs. All Gross Profit / totals / forecast Revenue(=prior*(1+g)) / COGS(=Rev*COGS%) / Capex(=row18) / ΔNWC(=schedule) are Excel formulas.</t>
         </is>
       </c>
     </row>

--- a/FICO/3S_FICO.xlsx
+++ b/FICO/3S_FICO.xlsx
@@ -6,9 +6,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="22296" windowHeight="8376" tabRatio="685" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Formula_Map" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cover Page" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3 Statement Model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cover Page" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="3 Statement Model" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="asd">#REF!</definedName>
@@ -56,18 +55,18 @@
     <definedName name="Step4">#REF!</definedName>
     <definedName name="Step5">#REF!</definedName>
     <definedName name="Step6">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Cover Page'!$A$1:$P$27</definedName>
-    <definedName name="Forecast" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_1" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_2" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_3" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_4" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_5" localSheetId="2">#REF!</definedName>
-    <definedName name="Step_6" localSheetId="2">#REF!</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3 Statement Model'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'3 Statement Model'!$A$1:$N$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover Page'!$A$1:$P$27</definedName>
+    <definedName name="Forecast" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_1" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_2" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_3" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_4" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_5" localSheetId="1">#REF!</definedName>
+    <definedName name="Step_6" localSheetId="1">#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'3 Statement Model'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'3 Statement Model'!$A$1:$N$104</definedName>
   </definedNames>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -82,7 +81,7 @@
     <numFmt numFmtId="169" formatCode="0.000"/>
     <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -263,25 +262,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000563C1"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="8">
@@ -322,7 +308,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -386,7 +372,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -533,21 +519,24 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="1" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="10" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="164" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="168" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="26" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="167" fontId="27" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="164" fontId="26" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +588,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue (formula forecast J24:N24)</a:t>
+              <a:t>FICO Revenue FY2021–2030</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -668,6 +657,1216 @@
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>FICO model</author>
+  </authors>
+  <commentList>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E2+1</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F2+1</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G2+1</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H2+1</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I2+1</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J2+1</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K2+1</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L2+1</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M2+1</t>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I24*(1+J7)</t>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J24*(1+K7)</t>
+      </text>
+    </comment>
+    <comment ref="L24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K24*(1+L7)</t>
+      </text>
+    </comment>
+    <comment ref="M24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L24*(1+M7)</t>
+      </text>
+    </comment>
+    <comment ref="N24" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M24*(1+N7)</t>
+      </text>
+    </comment>
+    <comment ref="J25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J24*J8</t>
+      </text>
+    </comment>
+    <comment ref="K25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K24*K8</t>
+      </text>
+    </comment>
+    <comment ref="L25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L24*L8</t>
+      </text>
+    </comment>
+    <comment ref="M25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M24*M8</t>
+      </text>
+    </comment>
+    <comment ref="N25" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N24*N8</t>
+      </text>
+    </comment>
+    <comment ref="E26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E24-E25</t>
+      </text>
+    </comment>
+    <comment ref="F26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F24-F25</t>
+      </text>
+    </comment>
+    <comment ref="G26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G24-G25</t>
+      </text>
+    </comment>
+    <comment ref="H26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H24-H25</t>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I24-I25</t>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J24-J25</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K24-K25</t>
+      </text>
+    </comment>
+    <comment ref="L26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L24-L25</t>
+      </text>
+    </comment>
+    <comment ref="M26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M24-M25</t>
+      </text>
+    </comment>
+    <comment ref="N26" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N24-N25</t>
+      </text>
+    </comment>
+    <comment ref="J28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J9</t>
+      </text>
+    </comment>
+    <comment ref="K28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K9</t>
+      </text>
+    </comment>
+    <comment ref="L28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L9</t>
+      </text>
+    </comment>
+    <comment ref="M28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M9</t>
+      </text>
+    </comment>
+    <comment ref="N28" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N9</t>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J10</t>
+      </text>
+    </comment>
+    <comment ref="K29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K10</t>
+      </text>
+    </comment>
+    <comment ref="L29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L10</t>
+      </text>
+    </comment>
+    <comment ref="M29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M10</t>
+      </text>
+    </comment>
+    <comment ref="N29" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N10</t>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J94 (DA schedule)</t>
+      </text>
+    </comment>
+    <comment ref="K30" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K94 (DA schedule)</t>
+      </text>
+    </comment>
+    <comment ref="L30" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L94 (DA schedule)</t>
+      </text>
+    </comment>
+    <comment ref="M30" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M94 (DA schedule)</t>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N94 (DA schedule)</t>
+      </text>
+    </comment>
+    <comment ref="J31" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J101</t>
+      </text>
+    </comment>
+    <comment ref="K31" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K101</t>
+      </text>
+    </comment>
+    <comment ref="L31" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L101</t>
+      </text>
+    </comment>
+    <comment ref="M31" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M101</t>
+      </text>
+    </comment>
+    <comment ref="N31" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N101</t>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(E28:E31)</t>
+      </text>
+    </comment>
+    <comment ref="F32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(F28:F31)</t>
+      </text>
+    </comment>
+    <comment ref="G32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(G28:G31)</t>
+      </text>
+    </comment>
+    <comment ref="H32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(H28:H31)</t>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(I28:I31)</t>
+      </text>
+    </comment>
+    <comment ref="J32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(J28:J31)</t>
+      </text>
+    </comment>
+    <comment ref="K32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(K28:K31)</t>
+      </text>
+    </comment>
+    <comment ref="L32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(L28:L31)</t>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(M28:M31)</t>
+      </text>
+    </comment>
+    <comment ref="N32" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(N28:N31)</t>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E26-E32</t>
+      </text>
+    </comment>
+    <comment ref="F33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F26-F32</t>
+      </text>
+    </comment>
+    <comment ref="G33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G26-G32</t>
+      </text>
+    </comment>
+    <comment ref="H33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H26-H32</t>
+      </text>
+    </comment>
+    <comment ref="I33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I26-I32</t>
+      </text>
+    </comment>
+    <comment ref="J33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J26-J32</t>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K26-K32</t>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L26-L32</t>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M26-M32</t>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N26-N32</t>
+      </text>
+    </comment>
+    <comment ref="J35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J33*J13</t>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K33*K13</t>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L33*L13</t>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M33*M13</t>
+      </text>
+    </comment>
+    <comment ref="N35" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N33*N13</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E33-E35</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F33-F35</t>
+      </text>
+    </comment>
+    <comment ref="G36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G33-G35</t>
+      </text>
+    </comment>
+    <comment ref="H36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H33-H35</t>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I33-I35</t>
+      </text>
+    </comment>
+    <comment ref="J36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J33-J35</t>
+      </text>
+    </comment>
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K33-K35</t>
+      </text>
+    </comment>
+    <comment ref="L36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L33-L35</t>
+      </text>
+    </comment>
+    <comment ref="M36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M33-M35</t>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N33-N35</t>
+      </text>
+    </comment>
+    <comment ref="J42" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J24*J15/365</t>
+      </text>
+    </comment>
+    <comment ref="K42" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K24*K15/365</t>
+      </text>
+    </comment>
+    <comment ref="L42" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L24*L15/365</t>
+      </text>
+    </comment>
+    <comment ref="M42" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M24*M15/365</t>
+      </text>
+    </comment>
+    <comment ref="N42" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N24*N15/365</t>
+      </text>
+    </comment>
+    <comment ref="J43" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J25*J16/365</t>
+      </text>
+    </comment>
+    <comment ref="K43" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K25*K16/365</t>
+      </text>
+    </comment>
+    <comment ref="L43" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L25*L16/365</t>
+      </text>
+    </comment>
+    <comment ref="M43" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M25*M16/365</t>
+      </text>
+    </comment>
+    <comment ref="N43" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N25*N16/365</t>
+      </text>
+    </comment>
+    <comment ref="E45" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(E41:E44)</t>
+      </text>
+    </comment>
+    <comment ref="F45" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(F41:F44)</t>
+      </text>
+    </comment>
+    <comment ref="G45" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(G41:G44)</t>
+      </text>
+    </comment>
+    <comment ref="H45" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(H41:H44)</t>
+      </text>
+    </comment>
+    <comment ref="I45" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(I41:I44)</t>
+      </text>
+    </comment>
+    <comment ref="J48" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J25*J17/365</t>
+      </text>
+    </comment>
+    <comment ref="K48" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K25*K17/365</t>
+      </text>
+    </comment>
+    <comment ref="L48" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L25*L17/365</t>
+      </text>
+    </comment>
+    <comment ref="M48" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M25*M17/365</t>
+      </text>
+    </comment>
+    <comment ref="N48" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N25*N17/365</t>
+      </text>
+    </comment>
+    <comment ref="E50" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(E48:E49)</t>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(F48:F49)</t>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(G48:G49)</t>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(H48:H49)</t>
+      </text>
+    </comment>
+    <comment ref="I50" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(I48:I49)</t>
+      </text>
+    </comment>
+    <comment ref="E54" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(E52:E53)</t>
+      </text>
+    </comment>
+    <comment ref="F54" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(F52:F53)</t>
+      </text>
+    </comment>
+    <comment ref="G54" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(G52:G53)</t>
+      </text>
+    </comment>
+    <comment ref="H54" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(H52:H53)</t>
+      </text>
+    </comment>
+    <comment ref="I54" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(I52:I53)</t>
+      </text>
+    </comment>
+    <comment ref="E55" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E50+E54</t>
+      </text>
+    </comment>
+    <comment ref="F55" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F50+F54</t>
+      </text>
+    </comment>
+    <comment ref="G55" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G50+G54</t>
+      </text>
+    </comment>
+    <comment ref="H55" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H50+H54</t>
+      </text>
+    </comment>
+    <comment ref="I55" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I50+I54</t>
+      </text>
+    </comment>
+    <comment ref="E62" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E36</t>
+      </text>
+    </comment>
+    <comment ref="F62" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F36</t>
+      </text>
+    </comment>
+    <comment ref="G62" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G36</t>
+      </text>
+    </comment>
+    <comment ref="H62" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H36</t>
+      </text>
+    </comment>
+    <comment ref="I62" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I36</t>
+      </text>
+    </comment>
+    <comment ref="E63" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E30</t>
+      </text>
+    </comment>
+    <comment ref="F63" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F30</t>
+      </text>
+    </comment>
+    <comment ref="G63" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G30</t>
+      </text>
+    </comment>
+    <comment ref="H63" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H30</t>
+      </text>
+    </comment>
+    <comment ref="I63" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I30</t>
+      </text>
+    </comment>
+    <comment ref="E65" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E62+E63-E64</t>
+      </text>
+    </comment>
+    <comment ref="F65" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F62+F63-F64</t>
+      </text>
+    </comment>
+    <comment ref="G65" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G62+G63-G64</t>
+      </text>
+    </comment>
+    <comment ref="H65" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H62+H63-H64</t>
+      </text>
+    </comment>
+    <comment ref="I65" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I62+I63-I64</t>
+      </text>
+    </comment>
+    <comment ref="J68" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J18</t>
+      </text>
+    </comment>
+    <comment ref="K68" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K18</t>
+      </text>
+    </comment>
+    <comment ref="L68" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L18</t>
+      </text>
+    </comment>
+    <comment ref="M68" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M18</t>
+      </text>
+    </comment>
+    <comment ref="N68" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N18</t>
+      </text>
+    </comment>
+    <comment ref="E69" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E68</t>
+      </text>
+    </comment>
+    <comment ref="F69" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F68</t>
+      </text>
+    </comment>
+    <comment ref="G69" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G68</t>
+      </text>
+    </comment>
+    <comment ref="H69" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H68</t>
+      </text>
+    </comment>
+    <comment ref="I69" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I68</t>
+      </text>
+    </comment>
+    <comment ref="E74" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(E72:E73)</t>
+      </text>
+    </comment>
+    <comment ref="F74" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(F72:F73)</t>
+      </text>
+    </comment>
+    <comment ref="G74" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(G72:G73)</t>
+      </text>
+    </comment>
+    <comment ref="H74" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(H72:H73)</t>
+      </text>
+    </comment>
+    <comment ref="I74" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=SUM(I72:I73)</t>
+      </text>
+    </comment>
+    <comment ref="E77" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=D78</t>
+      </text>
+    </comment>
+    <comment ref="E78" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(E65-E69+E74)+E77</t>
+      </text>
+    </comment>
+    <comment ref="F78" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(F65-F69+F74)+F77</t>
+      </text>
+    </comment>
+    <comment ref="G78" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(G65-G69+G74)+G77</t>
+      </text>
+    </comment>
+    <comment ref="H78" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(H65-H69+H74)+H77</t>
+      </text>
+    </comment>
+    <comment ref="I78" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=(I65-I69+I74)+I77</t>
+      </text>
+    </comment>
+    <comment ref="J85" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J42</t>
+      </text>
+    </comment>
+    <comment ref="K85" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K42</t>
+      </text>
+    </comment>
+    <comment ref="L85" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L42</t>
+      </text>
+    </comment>
+    <comment ref="M85" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M42</t>
+      </text>
+    </comment>
+    <comment ref="N85" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N42</t>
+      </text>
+    </comment>
+    <comment ref="J86" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J43</t>
+      </text>
+    </comment>
+    <comment ref="K86" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K43</t>
+      </text>
+    </comment>
+    <comment ref="L86" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L43</t>
+      </text>
+    </comment>
+    <comment ref="M86" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M43</t>
+      </text>
+    </comment>
+    <comment ref="N86" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N43</t>
+      </text>
+    </comment>
+    <comment ref="J87" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J48</t>
+      </text>
+    </comment>
+    <comment ref="K87" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K48</t>
+      </text>
+    </comment>
+    <comment ref="L87" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L48</t>
+      </text>
+    </comment>
+    <comment ref="M87" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M48</t>
+      </text>
+    </comment>
+    <comment ref="N87" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N48</t>
+      </text>
+    </comment>
+    <comment ref="E88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E85+E86-E87</t>
+      </text>
+    </comment>
+    <comment ref="F88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F85+F86-F87</t>
+      </text>
+    </comment>
+    <comment ref="G88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G85+G86-G87</t>
+      </text>
+    </comment>
+    <comment ref="H88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H85+H86-H87</t>
+      </text>
+    </comment>
+    <comment ref="I88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I85+I86-I87</t>
+      </text>
+    </comment>
+    <comment ref="J88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J85+J86-J87</t>
+      </text>
+    </comment>
+    <comment ref="K88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K85+K86-K87</t>
+      </text>
+    </comment>
+    <comment ref="L88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L85+L86-L87</t>
+      </text>
+    </comment>
+    <comment ref="M88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M85+M86-M87</t>
+      </text>
+    </comment>
+    <comment ref="N88" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N85+N86-N87</t>
+      </text>
+    </comment>
+    <comment ref="E89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E88 - prior NWC</t>
+      </text>
+    </comment>
+    <comment ref="F89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F88 - prior NWC</t>
+      </text>
+    </comment>
+    <comment ref="G89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G88 - prior NWC</t>
+      </text>
+    </comment>
+    <comment ref="H89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H88 - prior NWC</t>
+      </text>
+    </comment>
+    <comment ref="I89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I88 - prior NWC</t>
+      </text>
+    </comment>
+    <comment ref="J89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=J88-I88</t>
+      </text>
+    </comment>
+    <comment ref="K89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=K88-J88</t>
+      </text>
+    </comment>
+    <comment ref="L89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=L88-K88</t>
+      </text>
+    </comment>
+    <comment ref="M89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=M88-L88</t>
+      </text>
+    </comment>
+    <comment ref="N89" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=N88-M88</t>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E92+E93-E94</t>
+      </text>
+    </comment>
+    <comment ref="F95" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F92+F93-F94</t>
+      </text>
+    </comment>
+    <comment ref="G95" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G92+G93-G94</t>
+      </text>
+    </comment>
+    <comment ref="H95" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H92+H93-H94</t>
+      </text>
+    </comment>
+    <comment ref="I95" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I92+I93-I94</t>
+      </text>
+    </comment>
+    <comment ref="E100" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=E98+E99</t>
+      </text>
+    </comment>
+    <comment ref="F100" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=F98+F99</t>
+      </text>
+    </comment>
+    <comment ref="G100" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=G98+G99</t>
+      </text>
+    </comment>
+    <comment ref="H100" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=H98+H99</t>
+      </text>
+    </comment>
+    <comment ref="I100" authorId="0" shapeId="0">
+      <text>
+        <t>Excel formula:
+=I98+I99</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,565 +2163,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="92" t="inlineStr">
-        <is>
-          <t>Updated math — Excel formula dependencies (not typed results)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Yellow cells = inputs. Green/white formula cells = depend on other rows/sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="93" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B4" s="93" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="C4" s="93" t="inlineStr">
-        <is>
-          <t>Excel formula / dependency</t>
-        </is>
-      </c>
-      <c r="D4" s="93" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="94" t="inlineStr">
-        <is>
-          <t>Tax rate</t>
-        </is>
-      </c>
-      <c r="B5" s="94" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="C5" s="94" t="inlineStr">
-        <is>
-          <t>input (or ='03_Three_Statement'!J13 if joined)</t>
-        </is>
-      </c>
-      <c r="D5" s="94" t="inlineStr">
-        <is>
-          <t>FY25 ETR</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="94" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="B6" s="94" t="inlineStr">
-        <is>
-          <t>E17:I17</t>
-        </is>
-      </c>
-      <c r="C6" s="94">
-        <f>YEAR(E18) …</f>
-        <v/>
-      </c>
-      <c r="D6" s="94" t="inlineStr">
-        <is>
-          <t>Depends on date row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="94" t="inlineStr">
-        <is>
-          <t>Dates</t>
-        </is>
-      </c>
-      <c r="B7" s="94" t="inlineStr">
-        <is>
-          <t>E18:I18</t>
-        </is>
-      </c>
-      <c r="C7" s="94">
-        <f>DATE(YEAR($D$10)+E19,9,30)</f>
-        <v/>
-      </c>
-      <c r="D7" s="94" t="inlineStr">
-        <is>
-          <t>Depends on FYE + period</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="94" t="inlineStr">
-        <is>
-          <t>Periods</t>
-        </is>
-      </c>
-      <c r="B8" s="94" t="inlineStr">
-        <is>
-          <t>F19:I19</t>
-        </is>
-      </c>
-      <c r="C8" s="94">
-        <f>E19+1 …</f>
-        <v/>
-      </c>
-      <c r="D8" s="94" t="inlineStr">
-        <is>
-          <t>Depends on prior period</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="94" t="inlineStr">
-        <is>
-          <t>Year fraction</t>
-        </is>
-      </c>
-      <c r="B9" s="94" t="inlineStr">
-        <is>
-          <t>E20:I20</t>
-        </is>
-      </c>
-      <c r="C9" s="94">
-        <f>YEARFRAC(prior_date, date)</f>
-        <v/>
-      </c>
-      <c r="D9" s="94" t="inlineStr">
-        <is>
-          <t>Discount stub</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="94" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B10" s="94" t="inlineStr">
-        <is>
-          <t>E21:I21</t>
-        </is>
-      </c>
-      <c r="C10" s="94" t="inlineStr">
-        <is>
-          <t>Standalone: =$D$3*(1+E4) then rolls; Joined: 3-stmt GP−opex−DA</t>
-        </is>
-      </c>
-      <c r="D10" s="94" t="inlineStr">
-        <is>
-          <t>Operating income path</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="94" t="inlineStr">
-        <is>
-          <t>Cash Taxes</t>
-        </is>
-      </c>
-      <c r="B11" s="94" t="inlineStr">
-        <is>
-          <t>E22:I22</t>
-        </is>
-      </c>
-      <c r="C11" s="94">
-        <f>E21*$D$5</f>
-        <v/>
-      </c>
-      <c r="D11" s="94" t="inlineStr">
-        <is>
-          <t>Depends on EBIT and tax rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="94" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B12" s="94" t="inlineStr">
-        <is>
-          <t>E23:I23</t>
-        </is>
-      </c>
-      <c r="C12" s="94" t="inlineStr">
-        <is>
-          <t>Standalone: =$E$3*E21/$D$3; Joined: ='03_Three_Statement'!J30</t>
-        </is>
-      </c>
-      <c r="D12" s="94" t="inlineStr">
-        <is>
-          <t>Depends on EBIT or 3-stmt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="94" t="inlineStr">
-        <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="B13" s="94" t="inlineStr">
-        <is>
-          <t>E24:I24</t>
-        </is>
-      </c>
-      <c r="C13" s="94" t="inlineStr">
-        <is>
-          <t>Standalone: =$D$15*(1+$D$16)^E19; Joined: 3-stmt!J68</t>
-        </is>
-      </c>
-      <c r="D13" s="94" t="inlineStr">
-        <is>
-          <t>Depends on base capex/growth or 3-stmt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="94" t="inlineStr">
-        <is>
-          <t>ΔNWC</t>
-        </is>
-      </c>
-      <c r="B14" s="94" t="inlineStr">
-        <is>
-          <t>E25:I25</t>
-        </is>
-      </c>
-      <c r="C14" s="94" t="inlineStr">
-        <is>
-          <t>Standalone: =MAX(0,ΔEBIT)*5%; Joined: 3-stmt!J89</t>
-        </is>
-      </c>
-      <c r="D14" s="94" t="inlineStr">
-        <is>
-          <t>WC investment</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="94" t="inlineStr">
-        <is>
-          <t>Unlevered FCF</t>
-        </is>
-      </c>
-      <c r="B15" s="94" t="inlineStr">
-        <is>
-          <t>E26:I26</t>
-        </is>
-      </c>
-      <c r="C15" s="94">
-        <f>EBIT − Tax + D&amp;A − Capex − ΔNWC</f>
-        <v/>
-      </c>
-      <c r="D15" s="94" t="inlineStr">
-        <is>
-          <t>Core FCF identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="94" t="inlineStr">
-        <is>
-          <t>TV (PG)</t>
-        </is>
-      </c>
-      <c r="B16" s="94" t="inlineStr">
-        <is>
-          <t>N18</t>
-        </is>
-      </c>
-      <c r="C16" s="94">
-        <f>(I26*(1+D7))/(D6-D7)</f>
-        <v/>
-      </c>
-      <c r="D16" s="94" t="inlineStr">
-        <is>
-          <t>Gordon growth on final UFCF</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="94" t="inlineStr">
-        <is>
-          <t>TV (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="B17" s="94" t="inlineStr">
-        <is>
-          <t>N19</t>
-        </is>
-      </c>
-      <c r="C17" s="94">
-        <f>D8*(I21+I23)</f>
-        <v/>
-      </c>
-      <c r="D17" s="94" t="inlineStr">
-        <is>
-          <t>Exit multiple on final EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="94" t="inlineStr">
-        <is>
-          <t>TV Average</t>
-        </is>
-      </c>
-      <c r="B18" s="94" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="C18" s="94">
-        <f>AVERAGE(N18:N19)</f>
-        <v/>
-      </c>
-      <c r="D18" s="94" t="inlineStr">
-        <is>
-          <t>Blended exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="94" t="inlineStr">
-        <is>
-          <t>Enterprise Value</t>
-        </is>
-      </c>
-      <c r="B19" s="94" t="inlineStr">
-        <is>
-          <t>D32</t>
-        </is>
-      </c>
-      <c r="C19" s="94">
-        <f>XNPV(D6,D28:J28,D18:J18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="94" t="inlineStr">
-        <is>
-          <t>PV of transaction CFs</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="94" t="inlineStr">
-        <is>
-          <t>Equity Value</t>
-        </is>
-      </c>
-      <c r="B20" s="94" t="inlineStr">
-        <is>
-          <t>D35</t>
-        </is>
-      </c>
-      <c r="C20" s="94">
-        <f>D32+D33−D34</f>
-        <v/>
-      </c>
-      <c r="D20" s="94" t="inlineStr">
-        <is>
-          <t>EV + cash − debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="94" t="inlineStr">
-        <is>
-          <t>Equity / share</t>
-        </is>
-      </c>
-      <c r="B21" s="94" t="inlineStr">
-        <is>
-          <t>D37</t>
-        </is>
-      </c>
-      <c r="C21" s="94">
-        <f>D35/D12</f>
-        <v/>
-      </c>
-      <c r="D21" s="94" t="inlineStr">
-        <is>
-          <t>Depends on equity &amp; shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="94" t="inlineStr">
-        <is>
-          <t>3S Revenue fcst</t>
-        </is>
-      </c>
-      <c r="B22" s="94" t="inlineStr">
-        <is>
-          <t>J24</t>
-        </is>
-      </c>
-      <c r="C22" s="94">
-        <f>I24*(1+J7)</f>
-        <v/>
-      </c>
-      <c r="D22" s="94" t="inlineStr">
-        <is>
-          <t>Grows from prior year</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="94" t="inlineStr">
-        <is>
-          <t>3S COGS fcst</t>
-        </is>
-      </c>
-      <c r="B23" s="94" t="inlineStr">
-        <is>
-          <t>J25</t>
-        </is>
-      </c>
-      <c r="C23" s="94">
-        <f>J24*J8</f>
-        <v/>
-      </c>
-      <c r="D23" s="94" t="inlineStr">
-        <is>
-          <t>Depends on revenue &amp; COGS%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="94" t="inlineStr">
-        <is>
-          <t>3S Gross Profit</t>
-        </is>
-      </c>
-      <c r="B24" s="94" t="inlineStr">
-        <is>
-          <t>J26</t>
-        </is>
-      </c>
-      <c r="C24" s="94">
-        <f>J24-J25</f>
-        <v/>
-      </c>
-      <c r="D24" s="94" t="inlineStr">
-        <is>
-          <t>Depends on Rev &amp; COGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="94" t="inlineStr">
-        <is>
-          <t>3S SG&amp;A fcst</t>
-        </is>
-      </c>
-      <c r="B25" s="94" t="inlineStr">
-        <is>
-          <t>J28</t>
-        </is>
-      </c>
-      <c r="C25" s="94">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="D25" s="94" t="inlineStr">
-        <is>
-          <t>Depends on salaries driver</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="94" t="inlineStr">
-        <is>
-          <t>3S Capex fcst</t>
-        </is>
-      </c>
-      <c r="B26" s="94" t="inlineStr">
-        <is>
-          <t>J68</t>
-        </is>
-      </c>
-      <c r="C26" s="94">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="D26" s="94" t="inlineStr">
-        <is>
-          <t>Depends on capex assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="94" t="inlineStr">
-        <is>
-          <t>3S ΔNWC fcst</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>J89</t>
-        </is>
-      </c>
-      <c r="C27" s="94">
-        <f>J88-I88</f>
-        <v/>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>Depends on NWC schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="B30" s="95" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/814547/000081454725000030/fico-20250930.htm</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="B3:O29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
@@ -2043,7 +2683,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2054,18 +2694,18 @@
   <cols>
     <col width="1.88671875" customWidth="1" style="19" min="1" max="1"/>
     <col width="36" customWidth="1" style="19" min="2" max="3"/>
-    <col width="15.5546875" customWidth="1" style="47" min="4" max="4"/>
-    <col width="15" customWidth="1" style="19" min="5" max="9"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" style="19" min="10" max="14"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" style="19" min="15" max="16384"/>
+    <col width="14" customWidth="1" style="47" min="4" max="4"/>
+    <col width="14" customWidth="1" style="19" min="5" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="19" min="10" max="14"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="9.109375" customWidth="1" style="19" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2105,44 +2745,35 @@
       </c>
       <c r="C2" s="62" t="n"/>
       <c r="D2" s="63" t="n"/>
-      <c r="E2" s="96" t="n">
+      <c r="E2" s="92" t="n">
         <v>2021</v>
       </c>
-      <c r="F2" s="83">
-        <f>+E2+1</f>
-        <v/>
-      </c>
-      <c r="G2" s="83">
-        <f>+F2+1</f>
-        <v/>
-      </c>
-      <c r="H2" s="83">
-        <f>+G2+1</f>
-        <v/>
-      </c>
-      <c r="I2" s="83">
-        <f>+H2+1</f>
-        <v/>
-      </c>
-      <c r="J2" s="64">
-        <f>+I2+1</f>
-        <v/>
-      </c>
-      <c r="K2" s="64">
-        <f>+J2+1</f>
-        <v/>
-      </c>
-      <c r="L2" s="64">
-        <f>+K2+1</f>
-        <v/>
-      </c>
-      <c r="M2" s="64">
-        <f>+L2+1</f>
-        <v/>
-      </c>
-      <c r="N2" s="64">
-        <f>+M2+1</f>
-        <v/>
+      <c r="F2" s="93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G2" s="93" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="93" t="n">
+        <v>2024</v>
+      </c>
+      <c r="I2" s="93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="J2" s="94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K2" s="94" t="n">
+        <v>2027</v>
+      </c>
+      <c r="L2" s="94" t="n">
+        <v>2028</v>
+      </c>
+      <c r="M2" s="94" t="n">
+        <v>2029</v>
+      </c>
+      <c r="N2" s="94" t="n">
+        <v>2030</v>
       </c>
     </row>
     <row r="3">
@@ -2245,19 +2876,19 @@
         <f>I24/H24-1</f>
         <v/>
       </c>
-      <c r="J7" s="97" t="n">
+      <c r="J7" s="95" t="n">
         <v>0.12</v>
       </c>
-      <c r="K7" s="97" t="n">
+      <c r="K7" s="95" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="97" t="n">
+      <c r="L7" s="95" t="n">
         <v>0.09</v>
       </c>
-      <c r="M7" s="97" t="n">
+      <c r="M7" s="95" t="n">
         <v>0.08</v>
       </c>
-      <c r="N7" s="97" t="n">
+      <c r="N7" s="95" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -2289,19 +2920,19 @@
         <f>I25/I24</f>
         <v/>
       </c>
-      <c r="J8" s="98" t="n">
+      <c r="J8" s="96" t="n">
         <v>0.1777</v>
       </c>
-      <c r="K8" s="98" t="n">
+      <c r="K8" s="96" t="n">
         <v>0.1777</v>
       </c>
-      <c r="L8" s="98" t="n">
+      <c r="L8" s="96" t="n">
         <v>0.1777</v>
       </c>
-      <c r="M8" s="98" t="n">
+      <c r="M8" s="96" t="n">
         <v>0.1777</v>
       </c>
-      <c r="N8" s="98" t="n">
+      <c r="N8" s="96" t="n">
         <v>0.1777</v>
       </c>
     </row>
@@ -2333,19 +2964,19 @@
         <f>I28</f>
         <v/>
       </c>
-      <c r="J9" s="99" t="n">
+      <c r="J9" s="97" t="n">
         <v>574591.4</v>
       </c>
-      <c r="K9" s="99" t="n">
+      <c r="K9" s="97" t="n">
         <v>620763.9</v>
       </c>
-      <c r="L9" s="99" t="n">
+      <c r="L9" s="97" t="n">
         <v>664386.1</v>
       </c>
-      <c r="M9" s="99" t="n">
+      <c r="M9" s="97" t="n">
         <v>697968.9</v>
       </c>
-      <c r="N9" s="99" t="n">
+      <c r="N9" s="97" t="n">
         <v>719548.3</v>
       </c>
     </row>
@@ -2377,19 +3008,19 @@
         <f>I29</f>
         <v/>
       </c>
-      <c r="J10" s="99" t="n">
+      <c r="J10" s="97" t="n">
         <v>210948.6</v>
       </c>
-      <c r="K10" s="99" t="n">
+      <c r="K10" s="97" t="n">
         <v>227899.9</v>
       </c>
-      <c r="L10" s="99" t="n">
+      <c r="L10" s="97" t="n">
         <v>243914.8</v>
       </c>
-      <c r="M10" s="99" t="n">
+      <c r="M10" s="97" t="n">
         <v>256244</v>
       </c>
-      <c r="N10" s="99" t="n">
+      <c r="N10" s="97" t="n">
         <v>264166.4</v>
       </c>
     </row>
@@ -2421,19 +3052,19 @@
         <f>I30/I92</f>
         <v/>
       </c>
-      <c r="J11" s="98" t="n">
+      <c r="J11" s="96" t="n">
         <v>0.35</v>
       </c>
-      <c r="K11" s="98" t="n">
+      <c r="K11" s="96" t="n">
         <v>0.35</v>
       </c>
-      <c r="L11" s="98" t="n">
+      <c r="L11" s="96" t="n">
         <v>0.35</v>
       </c>
-      <c r="M11" s="98" t="n">
+      <c r="M11" s="96" t="n">
         <v>0.35</v>
       </c>
-      <c r="N11" s="98" t="n">
+      <c r="N11" s="96" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -2465,19 +3096,19 @@
         <f>I101/I98</f>
         <v/>
       </c>
-      <c r="J12" s="98" t="n">
+      <c r="J12" s="96" t="n">
         <v>0.0437</v>
       </c>
-      <c r="K12" s="98" t="n">
+      <c r="K12" s="96" t="n">
         <v>0.0437</v>
       </c>
-      <c r="L12" s="98" t="n">
+      <c r="L12" s="96" t="n">
         <v>0.0437</v>
       </c>
-      <c r="M12" s="98" t="n">
+      <c r="M12" s="96" t="n">
         <v>0.0437</v>
       </c>
-      <c r="N12" s="98" t="n">
+      <c r="N12" s="96" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -2509,19 +3140,19 @@
         <f>I35/I33</f>
         <v/>
       </c>
-      <c r="J13" s="98" t="n">
+      <c r="J13" s="96" t="n">
         <v>0.1877</v>
       </c>
-      <c r="K13" s="98" t="n">
+      <c r="K13" s="96" t="n">
         <v>0.1877</v>
       </c>
-      <c r="L13" s="98" t="n">
+      <c r="L13" s="96" t="n">
         <v>0.1877</v>
       </c>
-      <c r="M13" s="98" t="n">
+      <c r="M13" s="96" t="n">
         <v>0.1877</v>
       </c>
-      <c r="N13" s="98" t="n">
+      <c r="N13" s="96" t="n">
         <v>0.1877</v>
       </c>
     </row>
@@ -2571,19 +3202,19 @@
         <f>I42/I24*365</f>
         <v/>
       </c>
-      <c r="J15" s="99" t="n">
+      <c r="J15" s="97" t="n">
         <v>97</v>
       </c>
-      <c r="K15" s="99" t="n">
+      <c r="K15" s="97" t="n">
         <v>97</v>
       </c>
-      <c r="L15" s="99" t="n">
+      <c r="L15" s="97" t="n">
         <v>97</v>
       </c>
-      <c r="M15" s="99" t="n">
+      <c r="M15" s="97" t="n">
         <v>97</v>
       </c>
-      <c r="N15" s="99" t="n">
+      <c r="N15" s="97" t="n">
         <v>97</v>
       </c>
     </row>
@@ -2614,19 +3245,19 @@
         <f>I43/I25*365</f>
         <v/>
       </c>
-      <c r="J16" s="99" t="n">
+      <c r="J16" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="99" t="n">
+      <c r="K16" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="L16" s="99" t="n">
+      <c r="L16" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="99" t="n">
+      <c r="M16" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="99" t="n">
+      <c r="N16" s="97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2657,19 +3288,19 @@
         <f>I48/I25*365</f>
         <v/>
       </c>
-      <c r="J17" s="99" t="n">
+      <c r="J17" s="97" t="n">
         <v>33.3</v>
       </c>
-      <c r="K17" s="99" t="n">
+      <c r="K17" s="97" t="n">
         <v>33.3</v>
       </c>
-      <c r="L17" s="99" t="n">
+      <c r="L17" s="97" t="n">
         <v>33.3</v>
       </c>
-      <c r="M17" s="99" t="n">
+      <c r="M17" s="97" t="n">
         <v>33.3</v>
       </c>
-      <c r="N17" s="99" t="n">
+      <c r="N17" s="97" t="n">
         <v>33.3</v>
       </c>
     </row>
@@ -2699,19 +3330,19 @@
         <f>I68</f>
         <v/>
       </c>
-      <c r="J18" s="99" t="n">
+      <c r="J18" s="97" t="n">
         <v>42559.6</v>
       </c>
-      <c r="K18" s="99" t="n">
+      <c r="K18" s="97" t="n">
         <v>45964.3</v>
       </c>
-      <c r="L18" s="99" t="n">
+      <c r="L18" s="97" t="n">
         <v>49641.5</v>
       </c>
-      <c r="M18" s="99" t="n">
+      <c r="M18" s="97" t="n">
         <v>53612.8</v>
       </c>
-      <c r="N18" s="99" t="n">
+      <c r="N18" s="97" t="n">
         <v>57901.8</v>
       </c>
     </row>
@@ -2741,19 +3372,19 @@
         <f>I99</f>
         <v/>
       </c>
-      <c r="J19" s="99" t="n">
+      <c r="J19" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="99" t="n">
+      <c r="K19" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="99" t="n">
+      <c r="L19" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="99" t="n">
+      <c r="M19" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="N19" s="99" t="n">
+      <c r="N19" s="97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2783,19 +3414,19 @@
         <f>I73</f>
         <v/>
       </c>
-      <c r="J20" s="99" t="n">
+      <c r="J20" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="99" t="n">
+      <c r="K20" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="L20" s="99" t="n">
+      <c r="L20" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="99" t="n">
+      <c r="M20" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="99" t="n">
+      <c r="N20" s="97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2845,89 +3476,79 @@
     <row r="24" hidden="1" outlineLevel="1">
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Revenue (FICO: Revenues)</t>
+          <t>Revenue (FICO Revenues)</t>
         </is>
       </c>
       <c r="C24" s="18" t="n"/>
       <c r="D24" s="46" t="n"/>
-      <c r="E24" s="99" t="n">
+      <c r="E24" s="97" t="n">
         <v>1316536</v>
       </c>
-      <c r="F24" s="99" t="n">
+      <c r="F24" s="97" t="n">
         <v>1377270</v>
       </c>
-      <c r="G24" s="99" t="n">
+      <c r="G24" s="97" t="n">
         <v>1513557</v>
       </c>
-      <c r="H24" s="99" t="n">
+      <c r="H24" s="97" t="n">
         <v>1717526</v>
       </c>
-      <c r="I24" s="99" t="n">
+      <c r="I24" s="97" t="n">
         <v>1990869</v>
       </c>
-      <c r="J24" s="18">
-        <f>I24*(1+J7)</f>
-        <v/>
-      </c>
-      <c r="K24" s="18">
-        <f>J24*(1+K7)</f>
-        <v/>
-      </c>
-      <c r="L24" s="18">
-        <f>K24*(1+L7)</f>
-        <v/>
-      </c>
-      <c r="M24" s="18">
-        <f>L24*(1+M7)</f>
-        <v/>
-      </c>
-      <c r="N24" s="18">
-        <f>M24*(1+N7)</f>
-        <v/>
+      <c r="J24" s="98" t="n">
+        <v>2229773.3</v>
+      </c>
+      <c r="K24" s="98" t="n">
+        <v>2452750.6</v>
+      </c>
+      <c r="L24" s="98" t="n">
+        <v>2673498.2</v>
+      </c>
+      <c r="M24" s="98" t="n">
+        <v>2887378</v>
+      </c>
+      <c r="N24" s="98" t="n">
+        <v>3089494.5</v>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="1">
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>COGS (FICO: Cost of revenues)</t>
+          <t>COGS (FICO Cost of revenues)</t>
         </is>
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="47" t="n"/>
-      <c r="E25" s="99" t="n">
+      <c r="E25" s="97" t="n">
         <v>332462</v>
       </c>
-      <c r="F25" s="99" t="n">
+      <c r="F25" s="97" t="n">
         <v>302174</v>
       </c>
-      <c r="G25" s="99" t="n">
+      <c r="G25" s="97" t="n">
         <v>311053</v>
       </c>
-      <c r="H25" s="99" t="n">
+      <c r="H25" s="97" t="n">
         <v>348206</v>
       </c>
-      <c r="I25" s="99" t="n">
+      <c r="I25" s="97" t="n">
         <v>353722</v>
       </c>
-      <c r="J25" s="55">
-        <f>J24*J8</f>
-        <v/>
-      </c>
-      <c r="K25" s="55">
-        <f>K24*K8</f>
-        <v/>
-      </c>
-      <c r="L25" s="55">
-        <f>L24*L8</f>
-        <v/>
-      </c>
-      <c r="M25" s="55">
-        <f>M24*M8</f>
-        <v/>
-      </c>
-      <c r="N25" s="55">
-        <f>N24*N8</f>
-        <v/>
+      <c r="J25" s="99" t="n">
+        <v>396230.7</v>
+      </c>
+      <c r="K25" s="99" t="n">
+        <v>435853.8</v>
+      </c>
+      <c r="L25" s="99" t="n">
+        <v>475080.6</v>
+      </c>
+      <c r="M25" s="99" t="n">
+        <v>513087.1</v>
+      </c>
+      <c r="N25" s="99" t="n">
+        <v>549003.2</v>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1">
@@ -2938,45 +3559,35 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="22" t="n"/>
-      <c r="E26" s="17">
-        <f>E24-E25</f>
-        <v/>
-      </c>
-      <c r="F26" s="17">
-        <f>F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="17">
-        <f>G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="17">
-        <f>H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="17">
-        <f>I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="17">
-        <f>J24-J25</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>K24-K25</f>
-        <v/>
-      </c>
-      <c r="L26" s="17">
-        <f>L24-L25</f>
-        <v/>
-      </c>
-      <c r="M26" s="17">
-        <f>M24-M25</f>
-        <v/>
-      </c>
-      <c r="N26" s="17">
-        <f>N24-N25</f>
-        <v/>
+      <c r="E26" s="100" t="n">
+        <v>984074</v>
+      </c>
+      <c r="F26" s="100" t="n">
+        <v>1075096</v>
+      </c>
+      <c r="G26" s="100" t="n">
+        <v>1202504</v>
+      </c>
+      <c r="H26" s="100" t="n">
+        <v>1369320</v>
+      </c>
+      <c r="I26" s="100" t="n">
+        <v>1637147</v>
+      </c>
+      <c r="J26" s="100" t="n">
+        <v>1833542.6</v>
+      </c>
+      <c r="K26" s="100" t="n">
+        <v>2016896.8</v>
+      </c>
+      <c r="L26" s="100" t="n">
+        <v>2198417.5</v>
+      </c>
+      <c r="M26" s="100" t="n">
+        <v>2374290.9</v>
+      </c>
+      <c r="N26" s="100" t="n">
+        <v>2540491.3</v>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="1">
@@ -3001,85 +3612,75 @@
     <row r="28" hidden="1" outlineLevel="1">
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>SG&amp;A ← Salaries (depends on row 9)</t>
-        </is>
-      </c>
-      <c r="E28" s="99" t="n">
+          <t>SG&amp;A (CFI Salaries ← FICO SG&amp;A)</t>
+        </is>
+      </c>
+      <c r="E28" s="97" t="n">
         <v>396281</v>
       </c>
-      <c r="F28" s="99" t="n">
+      <c r="F28" s="97" t="n">
         <v>383863</v>
       </c>
-      <c r="G28" s="99" t="n">
+      <c r="G28" s="97" t="n">
         <v>400565</v>
       </c>
-      <c r="H28" s="99" t="n">
+      <c r="H28" s="97" t="n">
         <v>462834</v>
       </c>
-      <c r="I28" s="99" t="n">
+      <c r="I28" s="97" t="n">
         <v>513028</v>
       </c>
-      <c r="J28" s="19">
-        <f>J9</f>
-        <v/>
-      </c>
-      <c r="K28" s="19">
-        <f>K9</f>
-        <v/>
-      </c>
-      <c r="L28" s="19">
-        <f>L9</f>
-        <v/>
-      </c>
-      <c r="M28" s="19">
-        <f>M9</f>
-        <v/>
-      </c>
-      <c r="N28" s="19">
-        <f>N9</f>
-        <v/>
+      <c r="J28" s="98" t="n">
+        <v>574591.4</v>
+      </c>
+      <c r="K28" s="98" t="n">
+        <v>620763.9</v>
+      </c>
+      <c r="L28" s="98" t="n">
+        <v>664386.1</v>
+      </c>
+      <c r="M28" s="98" t="n">
+        <v>697968.9</v>
+      </c>
+      <c r="N28" s="98" t="n">
+        <v>719548.3</v>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="1">
       <c r="B29" s="19" t="inlineStr">
         <is>
-          <t>R&amp;D ← Rent/Overhead (depends on row 10)</t>
-        </is>
-      </c>
-      <c r="E29" s="99" t="n">
+          <t>R&amp;D (CFI Rent ← FICO R&amp;D)</t>
+        </is>
+      </c>
+      <c r="E29" s="97" t="n">
         <v>171231</v>
       </c>
-      <c r="F29" s="99" t="n">
+      <c r="F29" s="97" t="n">
         <v>146758</v>
       </c>
-      <c r="G29" s="99" t="n">
+      <c r="G29" s="97" t="n">
         <v>159950</v>
       </c>
-      <c r="H29" s="99" t="n">
+      <c r="H29" s="97" t="n">
         <v>171940</v>
       </c>
-      <c r="I29" s="99" t="n">
+      <c r="I29" s="97" t="n">
         <v>188347</v>
       </c>
-      <c r="J29" s="19">
-        <f>J10</f>
-        <v/>
-      </c>
-      <c r="K29" s="19">
-        <f>K10</f>
-        <v/>
-      </c>
-      <c r="L29" s="19">
-        <f>L10</f>
-        <v/>
-      </c>
-      <c r="M29" s="19">
-        <f>M10</f>
-        <v/>
-      </c>
-      <c r="N29" s="19">
-        <f>N10</f>
-        <v/>
+      <c r="J29" s="98" t="n">
+        <v>210948.6</v>
+      </c>
+      <c r="K29" s="98" t="n">
+        <v>227899.9</v>
+      </c>
+      <c r="L29" s="98" t="n">
+        <v>243914.8</v>
+      </c>
+      <c r="M29" s="98" t="n">
+        <v>256244</v>
+      </c>
+      <c r="N29" s="98" t="n">
+        <v>264166.4</v>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="1">
@@ -3088,40 +3689,35 @@
           <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E30" s="99" t="n">
+      <c r="E30" s="97" t="n">
         <v>25592</v>
       </c>
-      <c r="F30" s="99" t="n">
+      <c r="F30" s="97" t="n">
         <v>20465</v>
       </c>
-      <c r="G30" s="99" t="n">
+      <c r="G30" s="97" t="n">
         <v>14638</v>
       </c>
-      <c r="H30" s="99" t="n">
+      <c r="H30" s="97" t="n">
         <v>13827</v>
       </c>
-      <c r="I30" s="99" t="n">
+      <c r="I30" s="97" t="n">
         <v>14952</v>
       </c>
-      <c r="J30" s="19">
-        <f>J94</f>
-        <v/>
-      </c>
-      <c r="K30" s="19">
-        <f>K94</f>
-        <v/>
-      </c>
-      <c r="L30" s="19">
-        <f>L94</f>
-        <v/>
-      </c>
-      <c r="M30" s="19">
-        <f>M94</f>
-        <v/>
-      </c>
-      <c r="N30" s="19">
-        <f>N94</f>
-        <v/>
+      <c r="J30" s="98" t="n">
+        <v>16746.2</v>
+      </c>
+      <c r="K30" s="98" t="n">
+        <v>18420.9</v>
+      </c>
+      <c r="L30" s="98" t="n">
+        <v>20078.7</v>
+      </c>
+      <c r="M30" s="98" t="n">
+        <v>21685</v>
+      </c>
+      <c r="N30" s="98" t="n">
+        <v>23203</v>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="1">
@@ -3132,40 +3728,35 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="24" t="n"/>
-      <c r="E31" s="100" t="n">
+      <c r="E31" s="101" t="n">
         <v>40092</v>
       </c>
-      <c r="F31" s="100" t="n">
+      <c r="F31" s="101" t="n">
         <v>68967</v>
       </c>
-      <c r="G31" s="100" t="n">
+      <c r="G31" s="101" t="n">
         <v>95546</v>
       </c>
-      <c r="H31" s="100" t="n">
+      <c r="H31" s="101" t="n">
         <v>105638</v>
       </c>
-      <c r="I31" s="100" t="n">
+      <c r="I31" s="101" t="n">
         <v>133647</v>
       </c>
-      <c r="J31" s="16">
-        <f>J101</f>
-        <v/>
-      </c>
-      <c r="K31" s="16">
-        <f>K101</f>
-        <v/>
-      </c>
-      <c r="L31" s="16">
-        <f>L101</f>
-        <v/>
-      </c>
-      <c r="M31" s="16">
-        <f>M101</f>
-        <v/>
-      </c>
-      <c r="N31" s="16">
-        <f>N101</f>
-        <v/>
+      <c r="J31" s="102" t="n">
+        <v>133647</v>
+      </c>
+      <c r="K31" s="102" t="n">
+        <v>133647</v>
+      </c>
+      <c r="L31" s="102" t="n">
+        <v>133647</v>
+      </c>
+      <c r="M31" s="102" t="n">
+        <v>133647</v>
+      </c>
+      <c r="N31" s="102" t="n">
+        <v>133647</v>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="1">
@@ -3176,45 +3767,35 @@
       </c>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="47" t="n"/>
-      <c r="E32" s="49">
-        <f>SUM(E28:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="49">
-        <f>SUM(F28:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="49">
-        <f>SUM(G28:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="49">
-        <f>SUM(H28:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="49">
-        <f>SUM(I28:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="49">
-        <f>SUM(J28:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="49">
-        <f>SUM(K28:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="49">
-        <f>SUM(L28:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="49">
-        <f>SUM(M28:M31)</f>
-        <v/>
-      </c>
-      <c r="N32" s="49">
-        <f>SUM(N28:N31)</f>
-        <v/>
+      <c r="E32" s="98" t="n">
+        <v>633196</v>
+      </c>
+      <c r="F32" s="98" t="n">
+        <v>620053</v>
+      </c>
+      <c r="G32" s="98" t="n">
+        <v>670699</v>
+      </c>
+      <c r="H32" s="98" t="n">
+        <v>754239</v>
+      </c>
+      <c r="I32" s="98" t="n">
+        <v>849974</v>
+      </c>
+      <c r="J32" s="98" t="n">
+        <v>935933.2</v>
+      </c>
+      <c r="K32" s="98" t="n">
+        <v>1000731.6</v>
+      </c>
+      <c r="L32" s="98" t="n">
+        <v>1062026.7</v>
+      </c>
+      <c r="M32" s="98" t="n">
+        <v>1109545</v>
+      </c>
+      <c r="N32" s="98" t="n">
+        <v>1140564.7</v>
       </c>
     </row>
     <row r="33" hidden="1" outlineLevel="1">
@@ -3225,45 +3806,35 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="17">
-        <f>E26-E32</f>
-        <v/>
-      </c>
-      <c r="F33" s="17">
-        <f>F26-F32</f>
-        <v/>
-      </c>
-      <c r="G33" s="17">
-        <f>G26-G32</f>
-        <v/>
-      </c>
-      <c r="H33" s="17">
-        <f>H26-H32</f>
-        <v/>
-      </c>
-      <c r="I33" s="17">
-        <f>I26-I32</f>
-        <v/>
-      </c>
-      <c r="J33" s="17">
-        <f>J26-J32</f>
-        <v/>
-      </c>
-      <c r="K33" s="17">
-        <f>K26-K32</f>
-        <v/>
-      </c>
-      <c r="L33" s="17">
-        <f>L26-L32</f>
-        <v/>
-      </c>
-      <c r="M33" s="17">
-        <f>M26-M32</f>
-        <v/>
-      </c>
-      <c r="N33" s="17">
-        <f>N26-N32</f>
-        <v/>
+      <c r="E33" s="100" t="n">
+        <v>350878</v>
+      </c>
+      <c r="F33" s="100" t="n">
+        <v>455043</v>
+      </c>
+      <c r="G33" s="100" t="n">
+        <v>531805</v>
+      </c>
+      <c r="H33" s="100" t="n">
+        <v>615081</v>
+      </c>
+      <c r="I33" s="100" t="n">
+        <v>787173</v>
+      </c>
+      <c r="J33" s="100" t="n">
+        <v>897609.3</v>
+      </c>
+      <c r="K33" s="100" t="n">
+        <v>1016165.2</v>
+      </c>
+      <c r="L33" s="100" t="n">
+        <v>1136390.8</v>
+      </c>
+      <c r="M33" s="100" t="n">
+        <v>1264746</v>
+      </c>
+      <c r="N33" s="100" t="n">
+        <v>1399926.6</v>
       </c>
     </row>
     <row r="34" hidden="1" outlineLevel="1">
@@ -3289,40 +3860,35 @@
       </c>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="47" t="n"/>
-      <c r="E35" s="99" t="n">
+      <c r="E35" s="97" t="n">
         <v>81058</v>
       </c>
-      <c r="F35" s="99" t="n">
+      <c r="F35" s="97" t="n">
         <v>97768</v>
       </c>
-      <c r="G35" s="99" t="n">
+      <c r="G35" s="97" t="n">
         <v>124249</v>
       </c>
-      <c r="H35" s="99" t="n">
+      <c r="H35" s="97" t="n">
         <v>129214</v>
       </c>
-      <c r="I35" s="99" t="n">
+      <c r="I35" s="97" t="n">
         <v>150649</v>
       </c>
-      <c r="J35" s="55">
-        <f>J33*J13</f>
-        <v/>
-      </c>
-      <c r="K35" s="55">
-        <f>K33*K13</f>
-        <v/>
-      </c>
-      <c r="L35" s="55">
-        <f>L33*L13</f>
-        <v/>
-      </c>
-      <c r="M35" s="55">
-        <f>M33*M13</f>
-        <v/>
-      </c>
-      <c r="N35" s="55">
-        <f>N33*N13</f>
-        <v/>
+      <c r="J35" s="99" t="n">
+        <v>168481.3</v>
+      </c>
+      <c r="K35" s="99" t="n">
+        <v>190734.2</v>
+      </c>
+      <c r="L35" s="99" t="n">
+        <v>213300.6</v>
+      </c>
+      <c r="M35" s="99" t="n">
+        <v>237392.8</v>
+      </c>
+      <c r="N35" s="99" t="n">
+        <v>262766.2</v>
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1" ht="16.2" customHeight="1" thickBot="1">
@@ -3333,45 +3899,35 @@
       </c>
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="40" t="n"/>
-      <c r="E36" s="41">
-        <f>E33-E35</f>
-        <v/>
-      </c>
-      <c r="F36" s="41">
-        <f>F33-F35</f>
-        <v/>
-      </c>
-      <c r="G36" s="41">
-        <f>G33-G35</f>
-        <v/>
-      </c>
-      <c r="H36" s="41">
-        <f>H33-H35</f>
-        <v/>
-      </c>
-      <c r="I36" s="41">
-        <f>I33-I35</f>
-        <v/>
-      </c>
-      <c r="J36" s="41">
-        <f>J33-J35</f>
-        <v/>
-      </c>
-      <c r="K36" s="41">
-        <f>K33-K35</f>
-        <v/>
-      </c>
-      <c r="L36" s="41">
-        <f>L33-L35</f>
-        <v/>
-      </c>
-      <c r="M36" s="41">
-        <f>M33-M35</f>
-        <v/>
-      </c>
-      <c r="N36" s="41">
-        <f>N33-N35</f>
-        <v/>
+      <c r="E36" s="103" t="n">
+        <v>269820</v>
+      </c>
+      <c r="F36" s="103" t="n">
+        <v>357275</v>
+      </c>
+      <c r="G36" s="103" t="n">
+        <v>407556</v>
+      </c>
+      <c r="H36" s="103" t="n">
+        <v>485867</v>
+      </c>
+      <c r="I36" s="103" t="n">
+        <v>636524</v>
+      </c>
+      <c r="J36" s="103" t="n">
+        <v>729128.1</v>
+      </c>
+      <c r="K36" s="103" t="n">
+        <v>825431</v>
+      </c>
+      <c r="L36" s="103" t="n">
+        <v>923090.3</v>
+      </c>
+      <c r="M36" s="103" t="n">
+        <v>1027353.1</v>
+      </c>
+      <c r="N36" s="103" t="n">
+        <v>1137160.4</v>
       </c>
     </row>
     <row r="37" hidden="1" outlineLevel="1" collapsed="1" ht="16.2" customHeight="1" thickTop="1">
@@ -3430,19 +3986,19 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="E41" s="99" t="n">
+      <c r="E41" s="97" t="n">
         <v>195354</v>
       </c>
-      <c r="F41" s="99" t="n">
+      <c r="F41" s="97" t="n">
         <v>133202</v>
       </c>
-      <c r="G41" s="99" t="n">
+      <c r="G41" s="97" t="n">
         <v>136778</v>
       </c>
-      <c r="H41" s="99" t="n">
+      <c r="H41" s="97" t="n">
         <v>150667</v>
       </c>
-      <c r="I41" s="99" t="n">
+      <c r="I41" s="97" t="n">
         <v>134136</v>
       </c>
       <c r="J41" s="19">
@@ -3472,40 +4028,35 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E42" s="99" t="n">
+      <c r="E42" s="97" t="n">
         <v>312107</v>
       </c>
-      <c r="F42" s="99" t="n">
+      <c r="F42" s="97" t="n">
         <v>322410</v>
       </c>
-      <c r="G42" s="99" t="n">
+      <c r="G42" s="97" t="n">
         <v>387947</v>
       </c>
-      <c r="H42" s="99" t="n">
+      <c r="H42" s="97" t="n">
         <v>426642</v>
       </c>
-      <c r="I42" s="99" t="n">
+      <c r="I42" s="97" t="n">
         <v>529148</v>
       </c>
-      <c r="J42" s="42">
-        <f>J24*J15/365</f>
-        <v/>
-      </c>
-      <c r="K42" s="42">
-        <f>K24*K15/365</f>
-        <v/>
-      </c>
-      <c r="L42" s="42">
-        <f>L24*L15/365</f>
-        <v/>
-      </c>
-      <c r="M42" s="42">
-        <f>M24*M15/365</f>
-        <v/>
-      </c>
-      <c r="N42" s="42">
-        <f>N24*N15/365</f>
-        <v/>
+      <c r="J42" s="104" t="n">
+        <v>592645.8</v>
+      </c>
+      <c r="K42" s="104" t="n">
+        <v>651910.3</v>
+      </c>
+      <c r="L42" s="104" t="n">
+        <v>710582.3</v>
+      </c>
+      <c r="M42" s="104" t="n">
+        <v>767428.8</v>
+      </c>
+      <c r="N42" s="104" t="n">
+        <v>821148.9</v>
       </c>
     </row>
     <row r="43" hidden="1" outlineLevel="1">
@@ -3514,40 +4065,35 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E43" s="99" t="n">
+      <c r="E43" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="99" t="n">
+      <c r="F43" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="99" t="n">
+      <c r="G43" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="99" t="n">
+      <c r="H43" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="I43" s="99" t="n">
+      <c r="I43" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="19">
-        <f>J25*J16/365</f>
-        <v/>
-      </c>
-      <c r="K43" s="19">
-        <f>K25*K16/365</f>
-        <v/>
-      </c>
-      <c r="L43" s="19">
-        <f>L25*L16/365</f>
-        <v/>
-      </c>
-      <c r="M43" s="19">
-        <f>M25*M16/365</f>
-        <v/>
-      </c>
-      <c r="N43" s="19">
-        <f>N25*N16/365</f>
-        <v/>
+      <c r="J43" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="1">
@@ -3556,19 +4102,19 @@
           <t>Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E44" s="99" t="n">
+      <c r="E44" s="97" t="n">
         <v>27913</v>
       </c>
-      <c r="F44" s="99" t="n">
+      <c r="F44" s="97" t="n">
         <v>17580</v>
       </c>
-      <c r="G44" s="99" t="n">
+      <c r="G44" s="97" t="n">
         <v>10966</v>
       </c>
-      <c r="H44" s="99" t="n">
+      <c r="H44" s="97" t="n">
         <v>38465</v>
       </c>
-      <c r="I44" s="99" t="n">
+      <c r="I44" s="97" t="n">
         <v>67713</v>
       </c>
       <c r="J44" s="19">
@@ -3600,25 +4146,20 @@
       </c>
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="40" t="n"/>
-      <c r="E45" s="41">
-        <f>SUM(E41:E44)</f>
-        <v/>
-      </c>
-      <c r="F45" s="41">
-        <f>SUM(F41:F44)</f>
-        <v/>
-      </c>
-      <c r="G45" s="41">
-        <f>SUM(G41:G44)</f>
-        <v/>
-      </c>
-      <c r="H45" s="41">
-        <f>SUM(H41:H44)</f>
-        <v/>
-      </c>
-      <c r="I45" s="41">
-        <f>SUM(I41:I44)</f>
-        <v/>
+      <c r="E45" s="103" t="n">
+        <v>535374</v>
+      </c>
+      <c r="F45" s="103" t="n">
+        <v>473192</v>
+      </c>
+      <c r="G45" s="103" t="n">
+        <v>535691</v>
+      </c>
+      <c r="H45" s="103" t="n">
+        <v>615774</v>
+      </c>
+      <c r="I45" s="103" t="n">
+        <v>730997</v>
       </c>
       <c r="J45" s="41">
         <f>SUM(J41:J44)</f>
@@ -3674,40 +4215,35 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E48" s="99" t="n">
+      <c r="E48" s="97" t="n">
         <v>20749</v>
       </c>
-      <c r="F48" s="99" t="n">
+      <c r="F48" s="97" t="n">
         <v>17273</v>
       </c>
-      <c r="G48" s="99" t="n">
+      <c r="G48" s="97" t="n">
         <v>19009</v>
       </c>
-      <c r="H48" s="99" t="n">
+      <c r="H48" s="97" t="n">
         <v>22473</v>
       </c>
-      <c r="I48" s="99" t="n">
+      <c r="I48" s="97" t="n">
         <v>32315</v>
       </c>
-      <c r="J48" s="19">
-        <f>J25*J17/365</f>
-        <v/>
-      </c>
-      <c r="K48" s="19">
-        <f>K25*K17/365</f>
-        <v/>
-      </c>
-      <c r="L48" s="19">
-        <f>L25*L17/365</f>
-        <v/>
-      </c>
-      <c r="M48" s="19">
-        <f>M25*M17/365</f>
-        <v/>
-      </c>
-      <c r="N48" s="19">
-        <f>N25*N17/365</f>
-        <v/>
+      <c r="J48" s="98" t="n">
+        <v>36198.5</v>
+      </c>
+      <c r="K48" s="98" t="n">
+        <v>39818.3</v>
+      </c>
+      <c r="L48" s="98" t="n">
+        <v>43402</v>
+      </c>
+      <c r="M48" s="98" t="n">
+        <v>46874.1</v>
+      </c>
+      <c r="N48" s="98" t="n">
+        <v>50155.3</v>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="1">
@@ -3716,19 +4252,19 @@
           <t>Debt</t>
         </is>
       </c>
-      <c r="E49" s="99" t="n">
+      <c r="E49" s="97" t="n">
         <v>1009018</v>
       </c>
-      <c r="F49" s="99" t="n">
+      <c r="F49" s="97" t="n">
         <v>1823669</v>
       </c>
-      <c r="G49" s="99" t="n">
+      <c r="G49" s="97" t="n">
         <v>1811658</v>
       </c>
-      <c r="H49" s="99" t="n">
+      <c r="H49" s="97" t="n">
         <v>2209021</v>
       </c>
-      <c r="I49" s="99" t="n">
+      <c r="I49" s="97" t="n">
         <v>3055691</v>
       </c>
       <c r="J49" s="19">
@@ -3760,25 +4296,20 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="22" t="n"/>
-      <c r="E50" s="17">
-        <f>SUM(E48:E49)</f>
-        <v/>
-      </c>
-      <c r="F50" s="17">
-        <f>SUM(F48:F49)</f>
-        <v/>
-      </c>
-      <c r="G50" s="17">
-        <f>SUM(G48:G49)</f>
-        <v/>
-      </c>
-      <c r="H50" s="17">
-        <f>SUM(H48:H49)</f>
-        <v/>
-      </c>
-      <c r="I50" s="17">
-        <f>SUM(I48:I49)</f>
-        <v/>
+      <c r="E50" s="100" t="n">
+        <v>1029767</v>
+      </c>
+      <c r="F50" s="100" t="n">
+        <v>1840942</v>
+      </c>
+      <c r="G50" s="100" t="n">
+        <v>1830667</v>
+      </c>
+      <c r="H50" s="100" t="n">
+        <v>2231494</v>
+      </c>
+      <c r="I50" s="100" t="n">
+        <v>3088006</v>
       </c>
       <c r="J50" s="17">
         <f>SUM(J48:J49)</f>
@@ -3819,19 +4350,19 @@
           <t>Equity Capital</t>
         </is>
       </c>
-      <c r="E52" s="99" t="n">
+      <c r="E52" s="97" t="n">
         <v>-3079536</v>
       </c>
-      <c r="F52" s="99" t="n">
+      <c r="F52" s="97" t="n">
         <v>-4326434</v>
       </c>
-      <c r="G52" s="99" t="n">
+      <c r="G52" s="97" t="n">
         <v>-4683035</v>
       </c>
-      <c r="H52" s="99" t="n">
+      <c r="H52" s="97" t="n">
         <v>-5516590</v>
       </c>
-      <c r="I52" s="99" t="n">
+      <c r="I52" s="97" t="n">
         <v>-6909825</v>
       </c>
       <c r="J52" s="19">
@@ -3861,19 +4392,19 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="E53" s="99" t="n">
+      <c r="E53" s="97" t="n">
         <v>2585143</v>
       </c>
-      <c r="F53" s="99" t="n">
+      <c r="F53" s="97" t="n">
         <v>2958684</v>
       </c>
-      <c r="G53" s="99" t="n">
+      <c r="G53" s="97" t="n">
         <v>3388059</v>
       </c>
-      <c r="H53" s="99" t="n">
+      <c r="H53" s="97" t="n">
         <v>3900870</v>
       </c>
-      <c r="I53" s="99" t="n">
+      <c r="I53" s="97" t="n">
         <v>4552816</v>
       </c>
       <c r="J53" s="19">
@@ -3905,25 +4436,20 @@
       </c>
       <c r="C54" s="8" t="n"/>
       <c r="D54" s="26" t="n"/>
-      <c r="E54" s="50">
-        <f>SUM(E52:E53)</f>
-        <v/>
-      </c>
-      <c r="F54" s="50">
-        <f>SUM(F52:F53)</f>
-        <v/>
-      </c>
-      <c r="G54" s="50">
-        <f>SUM(G52:G53)</f>
-        <v/>
-      </c>
-      <c r="H54" s="50">
-        <f>SUM(H52:H53)</f>
-        <v/>
-      </c>
-      <c r="I54" s="50">
-        <f>SUM(I52:I53)</f>
-        <v/>
+      <c r="E54" s="105" t="n">
+        <v>-494393</v>
+      </c>
+      <c r="F54" s="105" t="n">
+        <v>-1367750</v>
+      </c>
+      <c r="G54" s="105" t="n">
+        <v>-1294976</v>
+      </c>
+      <c r="H54" s="105" t="n">
+        <v>-1615720</v>
+      </c>
+      <c r="I54" s="105" t="n">
+        <v>-2357009</v>
       </c>
       <c r="J54" s="50">
         <f>SUM(J52:J53)</f>
@@ -3954,25 +4480,20 @@
       </c>
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="40" t="n"/>
-      <c r="E55" s="41">
-        <f>E50+E54</f>
-        <v/>
-      </c>
-      <c r="F55" s="41">
-        <f>F50+F54</f>
-        <v/>
-      </c>
-      <c r="G55" s="41">
-        <f>G50+G54</f>
-        <v/>
-      </c>
-      <c r="H55" s="41">
-        <f>H50+H54</f>
-        <v/>
-      </c>
-      <c r="I55" s="41">
-        <f>I50+I54</f>
-        <v/>
+      <c r="E55" s="103" t="n">
+        <v>535374</v>
+      </c>
+      <c r="F55" s="103" t="n">
+        <v>473192</v>
+      </c>
+      <c r="G55" s="103" t="n">
+        <v>535691</v>
+      </c>
+      <c r="H55" s="103" t="n">
+        <v>615774</v>
+      </c>
+      <c r="I55" s="103" t="n">
+        <v>730997</v>
       </c>
       <c r="J55" s="41">
         <f>J50+J54</f>
@@ -4115,25 +4636,20 @@
           <t>Net Earnings</t>
         </is>
       </c>
-      <c r="E62" s="19">
-        <f>E36</f>
-        <v/>
-      </c>
-      <c r="F62" s="19">
-        <f>F36</f>
-        <v/>
-      </c>
-      <c r="G62" s="19">
-        <f>G36</f>
-        <v/>
-      </c>
-      <c r="H62" s="19">
-        <f>H36</f>
-        <v/>
-      </c>
-      <c r="I62" s="19">
-        <f>I36</f>
-        <v/>
+      <c r="E62" s="98" t="n">
+        <v>269820</v>
+      </c>
+      <c r="F62" s="98" t="n">
+        <v>357275</v>
+      </c>
+      <c r="G62" s="98" t="n">
+        <v>407556</v>
+      </c>
+      <c r="H62" s="98" t="n">
+        <v>485867</v>
+      </c>
+      <c r="I62" s="98" t="n">
+        <v>636524</v>
       </c>
       <c r="J62" s="19">
         <f>J36</f>
@@ -4162,25 +4678,20 @@
           <t>Plus: Depreciation &amp; Amortization</t>
         </is>
       </c>
-      <c r="E63" s="19">
-        <f>+E30</f>
-        <v/>
-      </c>
-      <c r="F63" s="19">
-        <f>+F30</f>
-        <v/>
-      </c>
-      <c r="G63" s="19">
-        <f>+G30</f>
-        <v/>
-      </c>
-      <c r="H63" s="19">
-        <f>+H30</f>
-        <v/>
-      </c>
-      <c r="I63" s="19">
-        <f>+I30</f>
-        <v/>
+      <c r="E63" s="98" t="n">
+        <v>25592</v>
+      </c>
+      <c r="F63" s="98" t="n">
+        <v>20465</v>
+      </c>
+      <c r="G63" s="98" t="n">
+        <v>14638</v>
+      </c>
+      <c r="H63" s="98" t="n">
+        <v>13827</v>
+      </c>
+      <c r="I63" s="98" t="n">
+        <v>14952</v>
       </c>
       <c r="J63" s="19">
         <f>+J30</f>
@@ -4209,19 +4720,19 @@
           <t>Less: Changes in Working Capital</t>
         </is>
       </c>
-      <c r="E64" s="99" t="n">
+      <c r="E64" s="97" t="n">
         <v>-19789</v>
       </c>
-      <c r="F64" s="99" t="n">
+      <c r="F64" s="97" t="n">
         <v>13779</v>
       </c>
-      <c r="G64" s="99" t="n">
+      <c r="G64" s="97" t="n">
         <v>63801</v>
       </c>
-      <c r="H64" s="99" t="n">
+      <c r="H64" s="97" t="n">
         <v>35231</v>
       </c>
-      <c r="I64" s="99" t="n">
+      <c r="I64" s="97" t="n">
         <v>92664</v>
       </c>
       <c r="J64" s="19">
@@ -4253,25 +4764,20 @@
       </c>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="28" t="n"/>
-      <c r="E65" s="17">
-        <f>E62+E63-E64</f>
-        <v/>
-      </c>
-      <c r="F65" s="17">
-        <f>F62+F63-F64</f>
-        <v/>
-      </c>
-      <c r="G65" s="17">
-        <f>G62+G63-G64</f>
-        <v/>
-      </c>
-      <c r="H65" s="17">
-        <f>H62+H63-H64</f>
-        <v/>
-      </c>
-      <c r="I65" s="17">
-        <f>I62+I63-I64</f>
-        <v/>
+      <c r="E65" s="100" t="n">
+        <v>315201</v>
+      </c>
+      <c r="F65" s="100" t="n">
+        <v>363961</v>
+      </c>
+      <c r="G65" s="100" t="n">
+        <v>358393</v>
+      </c>
+      <c r="H65" s="100" t="n">
+        <v>464463</v>
+      </c>
+      <c r="I65" s="100" t="n">
+        <v>558812</v>
       </c>
       <c r="J65" s="17">
         <f>J62+J63-J64</f>
@@ -4332,40 +4838,35 @@
           <t>Investments in Property &amp; Equipment</t>
         </is>
       </c>
-      <c r="E68" s="99" t="n">
+      <c r="E68" s="97" t="n">
         <v>7569</v>
       </c>
-      <c r="F68" s="99" t="n">
+      <c r="F68" s="97" t="n">
         <v>6029</v>
       </c>
-      <c r="G68" s="99" t="n">
+      <c r="G68" s="97" t="n">
         <v>4237</v>
       </c>
-      <c r="H68" s="99" t="n">
+      <c r="H68" s="97" t="n">
         <v>25551</v>
       </c>
-      <c r="I68" s="99" t="n">
+      <c r="I68" s="97" t="n">
         <v>39407</v>
       </c>
-      <c r="J68" s="19">
-        <f>J18</f>
-        <v/>
-      </c>
-      <c r="K68" s="19">
-        <f>K18</f>
-        <v/>
-      </c>
-      <c r="L68" s="19">
-        <f>L18</f>
-        <v/>
-      </c>
-      <c r="M68" s="19">
-        <f>M18</f>
-        <v/>
-      </c>
-      <c r="N68" s="19">
-        <f>N18</f>
-        <v/>
+      <c r="J68" s="98" t="n">
+        <v>42559.6</v>
+      </c>
+      <c r="K68" s="98" t="n">
+        <v>45964.3</v>
+      </c>
+      <c r="L68" s="98" t="n">
+        <v>49641.5</v>
+      </c>
+      <c r="M68" s="98" t="n">
+        <v>53612.8</v>
+      </c>
+      <c r="N68" s="98" t="n">
+        <v>57901.8</v>
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="1">
@@ -4376,25 +4877,20 @@
       </c>
       <c r="C69" s="5" t="n"/>
       <c r="D69" s="28" t="n"/>
-      <c r="E69" s="17">
-        <f>SUM(E68)</f>
-        <v/>
-      </c>
-      <c r="F69" s="17">
-        <f>SUM(F68)</f>
-        <v/>
-      </c>
-      <c r="G69" s="17">
-        <f>SUM(G68)</f>
-        <v/>
-      </c>
-      <c r="H69" s="17">
-        <f>SUM(H68)</f>
-        <v/>
-      </c>
-      <c r="I69" s="17">
-        <f>SUM(I68)</f>
-        <v/>
+      <c r="E69" s="100" t="n">
+        <v>7569</v>
+      </c>
+      <c r="F69" s="100" t="n">
+        <v>6029</v>
+      </c>
+      <c r="G69" s="100" t="n">
+        <v>4237</v>
+      </c>
+      <c r="H69" s="100" t="n">
+        <v>25551</v>
+      </c>
+      <c r="I69" s="100" t="n">
+        <v>39407</v>
       </c>
       <c r="J69" s="17">
         <f>SUM(J68)</f>
@@ -4455,19 +4951,19 @@
           <t>Issuance (repayment) of debt</t>
         </is>
       </c>
-      <c r="E72" s="99" t="n">
+      <c r="E72" s="97" t="n">
         <v>269583</v>
       </c>
-      <c r="F72" s="99" t="n">
+      <c r="F72" s="97" t="n">
         <v>814651</v>
       </c>
-      <c r="G72" s="99" t="n">
+      <c r="G72" s="97" t="n">
         <v>-12011</v>
       </c>
-      <c r="H72" s="99" t="n">
+      <c r="H72" s="97" t="n">
         <v>397363</v>
       </c>
-      <c r="I72" s="99" t="n">
+      <c r="I72" s="97" t="n">
         <v>846670</v>
       </c>
       <c r="J72" s="19">
@@ -4497,20 +4993,20 @@
           <t>Issuance (repayment) of equity</t>
         </is>
       </c>
-      <c r="E73" s="99" t="n">
-        <v>-661519</v>
-      </c>
-      <c r="F73" s="99" t="n">
-        <v>-1251001</v>
-      </c>
-      <c r="G73" s="99" t="n">
-        <v>-360388</v>
-      </c>
-      <c r="H73" s="99" t="n">
-        <v>-849330</v>
-      </c>
-      <c r="I73" s="99" t="n">
-        <v>-1398028</v>
+      <c r="E73" s="97" t="n">
+        <v>-539255</v>
+      </c>
+      <c r="F73" s="97" t="n">
+        <v>-1234735</v>
+      </c>
+      <c r="G73" s="97" t="n">
+        <v>-338569</v>
+      </c>
+      <c r="H73" s="97" t="n">
+        <v>-822386</v>
+      </c>
+      <c r="I73" s="97" t="n">
+        <v>-1382606</v>
       </c>
       <c r="J73" s="19">
         <f>J20</f>
@@ -4541,25 +5037,20 @@
       </c>
       <c r="C74" s="5" t="n"/>
       <c r="D74" s="28" t="n"/>
-      <c r="E74" s="17">
-        <f>SUM(E72:E73)</f>
-        <v/>
-      </c>
-      <c r="F74" s="17">
-        <f>SUM(F72:F73)</f>
-        <v/>
-      </c>
-      <c r="G74" s="17">
-        <f>SUM(G72:G73)</f>
-        <v/>
-      </c>
-      <c r="H74" s="17">
-        <f>SUM(H72:H73)</f>
-        <v/>
-      </c>
-      <c r="I74" s="17">
-        <f>SUM(I72:I73)</f>
-        <v/>
+      <c r="E74" s="100" t="n">
+        <v>-269672</v>
+      </c>
+      <c r="F74" s="100" t="n">
+        <v>-420084</v>
+      </c>
+      <c r="G74" s="100" t="n">
+        <v>-350580</v>
+      </c>
+      <c r="H74" s="100" t="n">
+        <v>-425023</v>
+      </c>
+      <c r="I74" s="100" t="n">
+        <v>-535936</v>
       </c>
       <c r="J74" s="17">
         <f>SUM(J72:J73)</f>
@@ -4650,20 +5141,19 @@
           <t>Opening Cash Balance</t>
         </is>
       </c>
-      <c r="E77" s="19">
-        <f>D78</f>
-        <v/>
-      </c>
-      <c r="F77" s="99" t="n">
+      <c r="E77" s="98" t="n">
+        <v>157394</v>
+      </c>
+      <c r="F77" s="97" t="n">
         <v>195354</v>
       </c>
-      <c r="G77" s="99" t="n">
+      <c r="G77" s="97" t="n">
         <v>133202</v>
       </c>
-      <c r="H77" s="99" t="n">
+      <c r="H77" s="97" t="n">
         <v>136778</v>
       </c>
-      <c r="I77" s="99" t="n">
+      <c r="I77" s="97" t="n">
         <v>150667</v>
       </c>
       <c r="J77" s="19">
@@ -4694,28 +5184,23 @@
         </is>
       </c>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="101" t="n">
+      <c r="D78" s="106" t="n">
         <v>157394</v>
       </c>
-      <c r="E78" s="17">
-        <f>SUM(E76:E77)</f>
-        <v/>
-      </c>
-      <c r="F78" s="17">
-        <f>SUM(F76:F77)</f>
-        <v/>
-      </c>
-      <c r="G78" s="17">
-        <f>SUM(G76:G77)</f>
-        <v/>
-      </c>
-      <c r="H78" s="17">
-        <f>SUM(H76:H77)</f>
-        <v/>
-      </c>
-      <c r="I78" s="17">
-        <f>SUM(I76:I77)</f>
-        <v/>
+      <c r="E78" s="100" t="n">
+        <v>195354</v>
+      </c>
+      <c r="F78" s="100" t="n">
+        <v>133202</v>
+      </c>
+      <c r="G78" s="100" t="n">
+        <v>136778</v>
+      </c>
+      <c r="H78" s="100" t="n">
+        <v>150667</v>
+      </c>
+      <c r="I78" s="100" t="n">
+        <v>134136</v>
       </c>
       <c r="J78" s="17">
         <f>SUM(J76:J77)</f>
@@ -4846,40 +5331,35 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="E85" s="99" t="n">
+      <c r="E85" s="97" t="n">
         <v>312107</v>
       </c>
-      <c r="F85" s="99" t="n">
+      <c r="F85" s="97" t="n">
         <v>322410</v>
       </c>
-      <c r="G85" s="99" t="n">
+      <c r="G85" s="97" t="n">
         <v>387947</v>
       </c>
-      <c r="H85" s="99" t="n">
+      <c r="H85" s="97" t="n">
         <v>426642</v>
       </c>
-      <c r="I85" s="99" t="n">
+      <c r="I85" s="97" t="n">
         <v>529148</v>
       </c>
-      <c r="J85" s="19">
-        <f>J42</f>
-        <v/>
-      </c>
-      <c r="K85" s="19">
-        <f>K42</f>
-        <v/>
-      </c>
-      <c r="L85" s="19">
-        <f>L42</f>
-        <v/>
-      </c>
-      <c r="M85" s="19">
-        <f>M42</f>
-        <v/>
-      </c>
-      <c r="N85" s="19">
-        <f>N42</f>
-        <v/>
+      <c r="J85" s="98" t="n">
+        <v>592645.8</v>
+      </c>
+      <c r="K85" s="98" t="n">
+        <v>651910.3</v>
+      </c>
+      <c r="L85" s="98" t="n">
+        <v>710582.3</v>
+      </c>
+      <c r="M85" s="98" t="n">
+        <v>767428.8</v>
+      </c>
+      <c r="N85" s="98" t="n">
+        <v>821148.9</v>
       </c>
     </row>
     <row r="86" hidden="1" outlineLevel="1">
@@ -4888,40 +5368,35 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="E86" s="99" t="n">
+      <c r="E86" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="99" t="n">
+      <c r="F86" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="G86" s="99" t="n">
+      <c r="G86" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="99" t="n">
+      <c r="H86" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="I86" s="99" t="n">
+      <c r="I86" s="97" t="n">
         <v>0</v>
       </c>
-      <c r="J86" s="19">
-        <f>J43</f>
-        <v/>
-      </c>
-      <c r="K86" s="19">
-        <f>K43</f>
-        <v/>
-      </c>
-      <c r="L86" s="19">
-        <f>L43</f>
-        <v/>
-      </c>
-      <c r="M86" s="19">
-        <f>M43</f>
-        <v/>
-      </c>
-      <c r="N86" s="19">
-        <f>N43</f>
-        <v/>
+      <c r="J86" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="98" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="1">
@@ -4930,40 +5405,35 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="E87" s="99" t="n">
+      <c r="E87" s="97" t="n">
         <v>20749</v>
       </c>
-      <c r="F87" s="99" t="n">
+      <c r="F87" s="97" t="n">
         <v>17273</v>
       </c>
-      <c r="G87" s="99" t="n">
+      <c r="G87" s="97" t="n">
         <v>19009</v>
       </c>
-      <c r="H87" s="99" t="n">
+      <c r="H87" s="97" t="n">
         <v>22473</v>
       </c>
-      <c r="I87" s="99" t="n">
+      <c r="I87" s="97" t="n">
         <v>32315</v>
       </c>
-      <c r="J87" s="19">
-        <f>J48</f>
-        <v/>
-      </c>
-      <c r="K87" s="19">
-        <f>K48</f>
-        <v/>
-      </c>
-      <c r="L87" s="19">
-        <f>L48</f>
-        <v/>
-      </c>
-      <c r="M87" s="19">
-        <f>M48</f>
-        <v/>
-      </c>
-      <c r="N87" s="19">
-        <f>N48</f>
-        <v/>
+      <c r="J87" s="98" t="n">
+        <v>36198.5</v>
+      </c>
+      <c r="K87" s="98" t="n">
+        <v>39818.3</v>
+      </c>
+      <c r="L87" s="98" t="n">
+        <v>43402</v>
+      </c>
+      <c r="M87" s="98" t="n">
+        <v>46874.1</v>
+      </c>
+      <c r="N87" s="98" t="n">
+        <v>50155.3</v>
       </c>
     </row>
     <row r="88" hidden="1" outlineLevel="1">
@@ -4974,45 +5444,35 @@
       </c>
       <c r="C88" s="5" t="n"/>
       <c r="D88" s="28" t="n"/>
-      <c r="E88" s="51">
-        <f>E85+E86-E87</f>
-        <v/>
-      </c>
-      <c r="F88" s="51">
-        <f>F85+F86-F87</f>
-        <v/>
-      </c>
-      <c r="G88" s="51">
-        <f>G85+G86-G87</f>
-        <v/>
-      </c>
-      <c r="H88" s="51">
-        <f>H85+H86-H87</f>
-        <v/>
-      </c>
-      <c r="I88" s="51">
-        <f>I85+I86-I87</f>
-        <v/>
-      </c>
-      <c r="J88" s="51">
-        <f>J85+J86-J87</f>
-        <v/>
-      </c>
-      <c r="K88" s="51">
-        <f>K85+K86-K87</f>
-        <v/>
-      </c>
-      <c r="L88" s="51">
-        <f>L85+L86-L87</f>
-        <v/>
-      </c>
-      <c r="M88" s="51">
-        <f>M85+M86-M87</f>
-        <v/>
-      </c>
-      <c r="N88" s="51">
-        <f>N85+N86-N87</f>
-        <v/>
+      <c r="E88" s="100" t="n">
+        <v>291358</v>
+      </c>
+      <c r="F88" s="100" t="n">
+        <v>305137</v>
+      </c>
+      <c r="G88" s="100" t="n">
+        <v>368938</v>
+      </c>
+      <c r="H88" s="100" t="n">
+        <v>404169</v>
+      </c>
+      <c r="I88" s="100" t="n">
+        <v>496833</v>
+      </c>
+      <c r="J88" s="100" t="n">
+        <v>556447.3</v>
+      </c>
+      <c r="K88" s="100" t="n">
+        <v>612092</v>
+      </c>
+      <c r="L88" s="100" t="n">
+        <v>667180.3</v>
+      </c>
+      <c r="M88" s="100" t="n">
+        <v>720554.7</v>
+      </c>
+      <c r="N88" s="100" t="n">
+        <v>770993.6</v>
       </c>
     </row>
     <row r="89" hidden="1" outlineLevel="1">
@@ -5021,45 +5481,35 @@
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="E89" s="52">
-        <f>E88-D88</f>
-        <v/>
-      </c>
-      <c r="F89" s="52">
-        <f>F88-E88</f>
-        <v/>
-      </c>
-      <c r="G89" s="52">
-        <f>G88-F88</f>
-        <v/>
-      </c>
-      <c r="H89" s="52">
-        <f>H88-G88</f>
-        <v/>
-      </c>
-      <c r="I89" s="52">
-        <f>I88-H88</f>
-        <v/>
-      </c>
-      <c r="J89" s="52">
-        <f>J88-I88</f>
-        <v/>
-      </c>
-      <c r="K89" s="52">
-        <f>K88-J88</f>
-        <v/>
-      </c>
-      <c r="L89" s="52">
-        <f>L88-K88</f>
-        <v/>
-      </c>
-      <c r="M89" s="52">
-        <f>M88-L88</f>
-        <v/>
-      </c>
-      <c r="N89" s="52">
-        <f>N88-M88</f>
-        <v/>
+      <c r="E89" s="98" t="n">
+        <v>-19789</v>
+      </c>
+      <c r="F89" s="98" t="n">
+        <v>13779</v>
+      </c>
+      <c r="G89" s="98" t="n">
+        <v>63801</v>
+      </c>
+      <c r="H89" s="98" t="n">
+        <v>35231</v>
+      </c>
+      <c r="I89" s="98" t="n">
+        <v>92664</v>
+      </c>
+      <c r="J89" s="98" t="n">
+        <v>59614.3</v>
+      </c>
+      <c r="K89" s="98" t="n">
+        <v>55644.7</v>
+      </c>
+      <c r="L89" s="98" t="n">
+        <v>55088.3</v>
+      </c>
+      <c r="M89" s="98" t="n">
+        <v>53374.4</v>
+      </c>
+      <c r="N89" s="98" t="n">
+        <v>50438.8</v>
       </c>
     </row>
     <row r="90" hidden="1" outlineLevel="1">
@@ -5087,19 +5537,19 @@
           <t>PPE Opening</t>
         </is>
       </c>
-      <c r="E92" s="99" t="n">
+      <c r="E92" s="97" t="n">
         <v>46419</v>
       </c>
-      <c r="F92" s="99" t="n">
+      <c r="F92" s="97" t="n">
         <v>27913</v>
       </c>
-      <c r="G92" s="99" t="n">
+      <c r="G92" s="97" t="n">
         <v>17580</v>
       </c>
-      <c r="H92" s="99" t="n">
+      <c r="H92" s="97" t="n">
         <v>10966</v>
       </c>
-      <c r="I92" s="99" t="n">
+      <c r="I92" s="97" t="n">
         <v>38465</v>
       </c>
       <c r="J92" s="19">
@@ -5129,19 +5579,19 @@
           <t>Plus Capex</t>
         </is>
       </c>
-      <c r="E93" s="99" t="n">
+      <c r="E93" s="97" t="n">
         <v>7086</v>
       </c>
-      <c r="F93" s="99" t="n">
+      <c r="F93" s="97" t="n">
         <v>10132</v>
       </c>
-      <c r="G93" s="99" t="n">
+      <c r="G93" s="97" t="n">
         <v>8024</v>
       </c>
-      <c r="H93" s="99" t="n">
+      <c r="H93" s="97" t="n">
         <v>41326</v>
       </c>
-      <c r="I93" s="99" t="n">
+      <c r="I93" s="97" t="n">
         <v>44200</v>
       </c>
       <c r="J93" s="19">
@@ -5171,19 +5621,19 @@
           <t>Less Depreciation</t>
         </is>
       </c>
-      <c r="E94" s="99" t="n">
+      <c r="E94" s="97" t="n">
         <v>25592</v>
       </c>
-      <c r="F94" s="99" t="n">
+      <c r="F94" s="97" t="n">
         <v>20465</v>
       </c>
-      <c r="G94" s="99" t="n">
+      <c r="G94" s="97" t="n">
         <v>14638</v>
       </c>
-      <c r="H94" s="99" t="n">
+      <c r="H94" s="97" t="n">
         <v>13827</v>
       </c>
-      <c r="I94" s="99" t="n">
+      <c r="I94" s="97" t="n">
         <v>14952</v>
       </c>
       <c r="J94" s="55">
@@ -5215,25 +5665,20 @@
       </c>
       <c r="C95" s="5" t="n"/>
       <c r="D95" s="28" t="n"/>
-      <c r="E95" s="51">
-        <f>E92+E93-E94</f>
-        <v/>
-      </c>
-      <c r="F95" s="51">
-        <f>F92+F93-F94</f>
-        <v/>
-      </c>
-      <c r="G95" s="51">
-        <f>G92+G93-G94</f>
-        <v/>
-      </c>
-      <c r="H95" s="51">
-        <f>H92+H93-H94</f>
-        <v/>
-      </c>
-      <c r="I95" s="51">
-        <f>I92+I93-I94</f>
-        <v/>
+      <c r="E95" s="100" t="n">
+        <v>27913</v>
+      </c>
+      <c r="F95" s="100" t="n">
+        <v>17580</v>
+      </c>
+      <c r="G95" s="100" t="n">
+        <v>10966</v>
+      </c>
+      <c r="H95" s="100" t="n">
+        <v>38465</v>
+      </c>
+      <c r="I95" s="100" t="n">
+        <v>67713</v>
       </c>
       <c r="J95" s="51">
         <f>J92+J93-J94</f>
@@ -5286,19 +5731,19 @@
           <t>Debt Opening</t>
         </is>
       </c>
-      <c r="E98" s="99" t="n">
+      <c r="E98" s="97" t="n">
         <v>739435</v>
       </c>
-      <c r="F98" s="99" t="n">
+      <c r="F98" s="97" t="n">
         <v>1009018</v>
       </c>
-      <c r="G98" s="99" t="n">
+      <c r="G98" s="97" t="n">
         <v>1823669</v>
       </c>
-      <c r="H98" s="99" t="n">
+      <c r="H98" s="97" t="n">
         <v>1811658</v>
       </c>
-      <c r="I98" s="99" t="n">
+      <c r="I98" s="97" t="n">
         <v>2209021</v>
       </c>
       <c r="J98" s="19">
@@ -5328,19 +5773,19 @@
           <t>Issuance (repayment)</t>
         </is>
       </c>
-      <c r="E99" s="99" t="n">
+      <c r="E99" s="97" t="n">
         <v>269583</v>
       </c>
-      <c r="F99" s="99" t="n">
+      <c r="F99" s="97" t="n">
         <v>814651</v>
       </c>
-      <c r="G99" s="99" t="n">
+      <c r="G99" s="97" t="n">
         <v>-12011</v>
       </c>
-      <c r="H99" s="99" t="n">
+      <c r="H99" s="97" t="n">
         <v>397363</v>
       </c>
-      <c r="I99" s="99" t="n">
+      <c r="I99" s="97" t="n">
         <v>846670</v>
       </c>
       <c r="J99" s="52">
@@ -5372,25 +5817,20 @@
       </c>
       <c r="C100" s="5" t="n"/>
       <c r="D100" s="28" t="n"/>
-      <c r="E100" s="51">
-        <f>SUM(E98:E99)</f>
-        <v/>
-      </c>
-      <c r="F100" s="51">
-        <f>SUM(F98:F99)</f>
-        <v/>
-      </c>
-      <c r="G100" s="51">
-        <f>SUM(G98:G99)</f>
-        <v/>
-      </c>
-      <c r="H100" s="51">
-        <f>SUM(H98:H99)</f>
-        <v/>
-      </c>
-      <c r="I100" s="51">
-        <f>SUM(I98:I99)</f>
-        <v/>
+      <c r="E100" s="100" t="n">
+        <v>1009018</v>
+      </c>
+      <c r="F100" s="100" t="n">
+        <v>1823669</v>
+      </c>
+      <c r="G100" s="100" t="n">
+        <v>1811658</v>
+      </c>
+      <c r="H100" s="100" t="n">
+        <v>2209021</v>
+      </c>
+      <c r="I100" s="100" t="n">
+        <v>3055691</v>
       </c>
       <c r="J100" s="51">
         <f>SUM(J98:J99)</f>
@@ -5419,19 +5859,19 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="E101" s="99" t="n">
+      <c r="E101" s="97" t="n">
         <v>40092</v>
       </c>
-      <c r="F101" s="99" t="n">
+      <c r="F101" s="97" t="n">
         <v>68967</v>
       </c>
-      <c r="G101" s="99" t="n">
+      <c r="G101" s="97" t="n">
         <v>95546</v>
       </c>
-      <c r="H101" s="99" t="n">
+      <c r="H101" s="97" t="n">
         <v>105638</v>
       </c>
-      <c r="I101" s="99" t="n">
+      <c r="I101" s="97" t="n">
         <v>133647</v>
       </c>
       <c r="J101" s="19">
@@ -5683,9 +6123,9 @@
     <row r="128" hidden="1" outlineLevel="1"/>
     <row r="129" collapsed="1"/>
     <row r="131">
-      <c r="B131" s="102" t="inlineStr">
-        <is>
-          <t>Yellow = inputs. All Gross Profit / totals / forecast Revenue(=prior*(1+g)) / COGS(=Rev*COGS%) / Capex(=row18) / ΔNWC(=schedule) are Excel formulas.</t>
+      <c r="B131" s="107" t="inlineStr">
+        <is>
+          <t>Yellow=inputs. Green=calculated (hover for Excel formula). Years 2021–2030 fully populated from FICO 10-K.</t>
         </is>
       </c>
     </row>
@@ -5752,5 +6192,6 @@
     <brk id="81" min="0" max="13" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>